--- a/dev_docs/千界万锻数值表格-V1.6-2025-10-8.xlsx
+++ b/dev_docs/千界万锻数值表格-V1.6-2025-10-8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PCL\.minecraft\versions\SenDims_BanForges\dev_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BD142D-8FC0-47CA-A5BF-A3BB7BD2FE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1706DE88-BE51-490C-B518-E0FB504973D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3950" yWindow="2820" windowWidth="19200" windowHeight="11260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="普通攻击" sheetId="1" r:id="rId1"/>
@@ -756,43 +756,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1068,40 +1068,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="5" max="5" width="10.90625" customWidth="1"/>
+    <col min="5" max="5" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="G1" s="42" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="G1" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>20</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>0</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A8" s="36" t="s">
         <v>9</v>
       </c>
@@ -1192,7 +1192,7 @@
       <c r="U8" s="37"/>
       <c r="V8" s="38"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1272,11 +1272,11 @@
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
         <v>9.0200000000000014</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="43">
         <f>D10+D11+D12+D13</f>
         <v>36.520000000000003</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="42">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1296,11 +1296,11 @@
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
         <v>9.0200000000000014</v>
       </c>
-      <c r="N10" s="39">
+      <c r="N10" s="43">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
         <v>50.338000000000008</v>
       </c>
-      <c r="O10" s="46">
+      <c r="O10" s="42">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -1320,12 +1320,12 @@
         <f>T10*R10</f>
         <v>9.0200000000000014</v>
       </c>
-      <c r="V10" s="43">
+      <c r="V10" s="39">
         <f>T10+T11+T12</f>
         <v>34.840000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1343,8 +1343,8 @@
         <f t="shared" si="0"/>
         <v>9.0200000000000014</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="42"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1362,8 +1362,8 @@
         <f t="shared" si="2"/>
         <v>9.0200000000000014</v>
       </c>
-      <c r="N11" s="40"/>
-      <c r="O11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="42"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1381,9 +1381,9 @@
         <f>T11*R11</f>
         <v>9.0200000000000014</v>
       </c>
-      <c r="V11" s="44"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V11" s="40"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1401,8 +1401,8 @@
         <f t="shared" si="0"/>
         <v>18.48</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="42"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1420,8 +1420,8 @@
         <f t="shared" si="2"/>
         <v>18.48</v>
       </c>
-      <c r="N12" s="40"/>
-      <c r="O12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="42"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -1439,9 +1439,9 @@
         <f>T12*R12</f>
         <v>33.6</v>
       </c>
-      <c r="V12" s="45"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V12" s="41"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -1459,8 +1459,8 @@
         <f t="shared" si="0"/>
         <v>18.48</v>
       </c>
-      <c r="F13" s="41"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="42"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -1478,10 +1478,10 @@
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="N13" s="40"/>
-      <c r="O13" s="46"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N13" s="46"/>
+      <c r="O13" s="42"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -1499,11 +1499,11 @@
         <f t="shared" si="0"/>
         <v>31.5</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="43">
         <f>D10+D11+D12+D14+D15</f>
         <v>59.155000000000001</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="42">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -1523,10 +1523,10 @@
         <f t="shared" si="2"/>
         <v>40.137999999999998</v>
       </c>
-      <c r="N14" s="40"/>
-      <c r="O14" s="46"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N14" s="46"/>
+      <c r="O14" s="42"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -1544,8 +1544,8 @@
         <f t="shared" si="0"/>
         <v>48.375</v>
       </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="42"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -1563,10 +1563,10 @@
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="N15" s="40"/>
-      <c r="O15" s="46"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N15" s="46"/>
+      <c r="O15" s="42"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
         <v>37</v>
       </c>
@@ -1595,10 +1595,10 @@
         <f t="shared" si="2"/>
         <v>10.247999999999999</v>
       </c>
-      <c r="N16" s="41"/>
-      <c r="O16" s="46"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N16" s="44"/>
+      <c r="O16" s="42"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
         <v>38</v>
       </c>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="O17" s="5"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
       <c r="E18" s="6" t="s">
         <v>40</v>
       </c>
@@ -1640,11 +1640,11 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A20" s="36" t="s">
         <v>29</v>
       </c>
@@ -1662,7 +1662,7 @@
       <c r="N20" s="38"/>
       <c r="O20" s="5"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="O21" s="5"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -1732,13 +1732,13 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="43">
+      <c r="N22" s="39">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
       <c r="O22" s="5"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -1772,10 +1772,10 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="44"/>
+      <c r="N23" s="40"/>
       <c r="O23" s="5"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -1809,10 +1809,10 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="45"/>
+      <c r="N24" s="41"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -1846,13 +1846,13 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="43">
+      <c r="N25" s="39">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
       <c r="I26" s="1" t="s">
         <v>25</v>
       </c>
@@ -1869,21 +1869,21 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="45"/>
+      <c r="N26" s="41"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="47" t="s">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A30" s="45" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="37"/>
@@ -1892,7 +1892,7 @@
       <c r="E30" s="37"/>
       <c r="F30" s="38"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="47" t="s">
+      <c r="I30" s="45" t="s">
         <v>44</v>
       </c>
       <c r="J30" s="37"/>
@@ -1902,7 +1902,7 @@
       <c r="N30" s="38"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>12</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>18</v>
       </c>
@@ -1964,11 +1964,11 @@
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
         <v>14.145</v>
       </c>
-      <c r="F32" s="39">
+      <c r="F32" s="43">
         <f>D32+D33+D34+D35</f>
         <v>57.269999999999996</v>
       </c>
-      <c r="G32" s="46">
+      <c r="G32" s="42">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -1988,15 +1988,15 @@
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
         <v>14.145</v>
       </c>
-      <c r="N32" s="39">
+      <c r="N32" s="43">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
         <v>89.46299999999998</v>
       </c>
-      <c r="O32" s="46">
+      <c r="O32" s="42">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -2014,8 +2014,8 @@
         <f t="shared" si="4"/>
         <v>14.145</v>
       </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="42"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -2033,10 +2033,10 @@
         <f t="shared" si="6"/>
         <v>14.145</v>
       </c>
-      <c r="N33" s="40"/>
-      <c r="O33" s="46"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N33" s="46"/>
+      <c r="O33" s="42"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>20</v>
       </c>
@@ -2054,8 +2054,8 @@
         <f t="shared" si="4"/>
         <v>28.979999999999997</v>
       </c>
-      <c r="F34" s="40"/>
-      <c r="G34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="42"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -2073,10 +2073,10 @@
         <f t="shared" si="6"/>
         <v>28.979999999999997</v>
       </c>
-      <c r="N34" s="40"/>
-      <c r="O34" s="46"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N34" s="46"/>
+      <c r="O34" s="42"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>22</v>
       </c>
@@ -2094,8 +2094,8 @@
         <f t="shared" si="4"/>
         <v>28.979999999999997</v>
       </c>
-      <c r="F35" s="41"/>
-      <c r="G35" s="46"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="42"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -2113,10 +2113,10 @@
         <f t="shared" si="6"/>
         <v>123.49999999999997</v>
       </c>
-      <c r="N35" s="40"/>
-      <c r="O35" s="46"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N35" s="46"/>
+      <c r="O35" s="42"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>24</v>
       </c>
@@ -2134,11 +2134,11 @@
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="43">
         <f>D32+D33+D34+D36+D37</f>
         <v>85.28</v>
       </c>
-      <c r="G36" s="46">
+      <c r="G36" s="42">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -2158,10 +2158,10 @@
         <f t="shared" si="6"/>
         <v>81.262999999999991</v>
       </c>
-      <c r="N36" s="40"/>
-      <c r="O36" s="46"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N36" s="46"/>
+      <c r="O36" s="42"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>26</v>
       </c>
@@ -2179,8 +2179,8 @@
         <f t="shared" si="4"/>
         <v>64.5</v>
       </c>
-      <c r="F37" s="41"/>
-      <c r="G37" s="46"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="42"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -2198,10 +2198,10 @@
         <f t="shared" si="6"/>
         <v>123.49999999999997</v>
       </c>
-      <c r="N37" s="40"/>
-      <c r="O37" s="46"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N37" s="46"/>
+      <c r="O37" s="42"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
         <v>37</v>
       </c>
@@ -2230,10 +2230,10 @@
         <f t="shared" si="6"/>
         <v>20.747999999999998</v>
       </c>
-      <c r="N38" s="41"/>
-      <c r="O38" s="46"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N38" s="44"/>
+      <c r="O38" s="42"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
         <v>38</v>
       </c>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="O39" s="5"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
       <c r="E40" s="6" t="s">
         <v>40</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A43" s="36" t="s">
         <v>29</v>
       </c>
@@ -2292,7 +2292,7 @@
       <c r="M43" s="37"/>
       <c r="N43" s="38"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>12</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>31</v>
       </c>
@@ -2361,12 +2361,12 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="43">
+      <c r="N45" s="39">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>32</v>
       </c>
@@ -2400,9 +2400,9 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="44"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N46" s="40"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>33</v>
       </c>
@@ -2436,9 +2436,9 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="45"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N47" s="41"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>34</v>
       </c>
@@ -2472,12 +2472,12 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="43">
+      <c r="N48" s="39">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
     </row>
-    <row r="49" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="9:14" x14ac:dyDescent="0.15">
       <c r="I49" s="1" t="s">
         <v>25</v>
       </c>
@@ -2494,29 +2494,10 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="45"/>
+      <c r="N49" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -2526,6 +2507,25 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2536,7 +2536,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2547,12 +2547,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:AZ21"/>
-  <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="15.6328125" style="8"/>
+    <col min="1" max="16384" width="15.625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D1" s="27" t="s">
         <v>65</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D2" s="27">
         <v>0.5</v>
       </c>
@@ -2592,62 +2592,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="50" t="s">
+      <c r="V3" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="50"/>
-      <c r="AD3" s="50"/>
-      <c r="AE3" s="50"/>
-      <c r="AF3" s="50"/>
-      <c r="AG3" s="50"/>
-      <c r="AH3" s="50"/>
-      <c r="AI3" s="50"/>
-      <c r="AJ3" s="50"/>
-      <c r="AK3" s="50"/>
-      <c r="AL3" s="50"/>
-      <c r="AM3" s="50"/>
-      <c r="AN3" s="50"/>
-      <c r="AO3" s="50"/>
-      <c r="AP3" s="50"/>
-      <c r="AQ3" s="50"/>
-      <c r="AR3" s="50"/>
-      <c r="AS3" s="50"/>
-      <c r="AT3" s="50"/>
-      <c r="AU3" s="50"/>
-      <c r="AV3" s="50"/>
-      <c r="AW3" s="50"/>
-      <c r="AX3" s="50"/>
-      <c r="AY3" s="50"/>
+      <c r="W3" s="48"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="48"/>
+      <c r="Z3" s="48"/>
+      <c r="AA3" s="48"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="48"/>
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="48"/>
+      <c r="AI3" s="48"/>
+      <c r="AJ3" s="48"/>
+      <c r="AK3" s="48"/>
+      <c r="AL3" s="48"/>
+      <c r="AM3" s="48"/>
+      <c r="AN3" s="48"/>
+      <c r="AO3" s="48"/>
+      <c r="AP3" s="48"/>
+      <c r="AQ3" s="48"/>
+      <c r="AR3" s="48"/>
+      <c r="AS3" s="48"/>
+      <c r="AT3" s="48"/>
+      <c r="AU3" s="48"/>
+      <c r="AV3" s="48"/>
+      <c r="AW3" s="48"/>
+      <c r="AX3" s="48"/>
+      <c r="AY3" s="48"/>
       <c r="AZ3" s="21"/>
     </row>
-    <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="21" t="s">
         <v>71</v>
       </c>
@@ -2690,47 +2690,47 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="51" t="s">
+      <c r="V4" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="51"/>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="W4" s="49"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="49"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="51" t="s">
+      <c r="AD4" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="51"/>
+      <c r="AE4" s="49"/>
+      <c r="AF4" s="49"/>
+      <c r="AG4" s="49"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="51" t="s">
+      <c r="AL4" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="51"/>
-      <c r="AN4" s="51"/>
-      <c r="AO4" s="51"/>
-      <c r="AP4" s="51"/>
-      <c r="AQ4" s="51"/>
+      <c r="AM4" s="49"/>
+      <c r="AN4" s="49"/>
+      <c r="AO4" s="49"/>
+      <c r="AP4" s="49"/>
+      <c r="AQ4" s="49"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="51" t="s">
+      <c r="AT4" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="51"/>
-      <c r="AV4" s="51"/>
-      <c r="AW4" s="51"/>
-      <c r="AX4" s="51"/>
-      <c r="AY4" s="51"/>
+      <c r="AU4" s="49"/>
+      <c r="AV4" s="49"/>
+      <c r="AW4" s="49"/>
+      <c r="AX4" s="49"/>
+      <c r="AY4" s="49"/>
       <c r="AZ4" s="21"/>
     </row>
-    <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="19"/>
       <c r="D5" s="12" t="s">
         <v>49</v>
@@ -2868,8 +2868,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="48">
+    <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="50">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -3029,8 +3029,8 @@
         <v>2.0438194898626554</v>
       </c>
     </row>
-    <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="48"/>
+    <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="50"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -3188,8 +3188,8 @@
         <v>2.4096681142200214</v>
       </c>
     </row>
-    <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="48">
+    <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="50">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -3349,8 +3349,8 @@
         <v>2.9137714374111283</v>
       </c>
     </row>
-    <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
+    <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="50"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -3508,8 +3508,8 @@
         <v>3.1948765134586452</v>
       </c>
     </row>
-    <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="49">
+    <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="51">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3669,11 +3669,11 @@
         <v>3.1176630995058288</v>
       </c>
     </row>
-    <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="49"/>
-    </row>
-    <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="49"/>
+    <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="51"/>
+    </row>
+    <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="51"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3831,8 +3831,8 @@
         <v>3.1787843692815017</v>
       </c>
     </row>
-    <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="48">
+    <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="50">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -3992,8 +3992,8 @@
         <v>3.4266478063971411</v>
       </c>
     </row>
-    <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
+    <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="50"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -4151,8 +4151,8 @@
         <v>3.5788579551928295</v>
       </c>
     </row>
-    <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="48">
+    <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="50">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -4312,8 +4312,8 @@
         <v>3.5334972210915043</v>
       </c>
     </row>
-    <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="48"/>
+    <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="50"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -4471,8 +4471,8 @@
         <v>3.5933509739225009</v>
       </c>
     </row>
-    <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="48"/>
+    <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="50"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4630,8 +4630,8 @@
         <v>3.5600496082328954</v>
       </c>
     </row>
-    <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="48">
+    <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="50">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -4791,8 +4791,8 @@
         <v>3.7358094278220939</v>
       </c>
     </row>
-    <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="48"/>
+    <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="50"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -4952,18 +4952,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="D3:P3"/>
     <mergeCell ref="V3:AY3"/>
     <mergeCell ref="AT4:AY4"/>
     <mergeCell ref="AL4:AQ4"/>
     <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="V4:AA4"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_docs/千界万锻数值表格-V1.6-2025-10-8.xlsx
+++ b/dev_docs/千界万锻数值表格-V1.6-2025-10-8.xlsx
@@ -5,30 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\SDBF\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1706DE88-BE51-490C-B518-E0FB504973D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93322935-1AFA-45C8-9FF3-ABBEEAFAEA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="普通攻击" sheetId="1" r:id="rId1"/>
-    <sheet name="技能" sheetId="2" r:id="rId2"/>
-    <sheet name="数值分配" sheetId="3" r:id="rId3"/>
+    <sheet name="数值分配" sheetId="3" r:id="rId2"/>
+    <sheet name="技能" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -756,6 +745,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -768,31 +769,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1074,32 +1063,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="G1" s="47" t="s">
+      <c r="A1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="G1" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -1123,7 +1112,7 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -1136,7 +1125,7 @@
       </c>
       <c r="E3" s="9">
         <f>A3+B3+(C3/2)+D3</f>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0.5</v>
@@ -1266,17 +1255,17 @@
       </c>
       <c r="D10" s="1">
         <f>MAX($I$3,($E$3*C10-$A$6)+(($E$3*C10*$C$6-$A$6)-($E$3*C10-$A$6))*$B$6)</f>
-        <v>9.0200000000000014</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="9">
         <f t="shared" ref="E10:E15" si="0">D10*B10</f>
-        <v>9.0200000000000014</v>
-      </c>
-      <c r="F10" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="39">
         <f>D10+D11+D12+D13</f>
-        <v>36.520000000000003</v>
-      </c>
-      <c r="G10" s="42">
+        <v>2</v>
+      </c>
+      <c r="G10" s="46">
         <v>1.5</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1290,17 +1279,17 @@
       </c>
       <c r="L10" s="1">
         <f t="shared" ref="L10:L16" si="1">MAX($I$3,($E$3*K10-$A$6)+(($E$3*K10*$C$6-$A$6)-($E$3*K10-$A$6))*$B$6*J10)</f>
-        <v>9.0200000000000014</v>
+        <v>0.5</v>
       </c>
       <c r="M10" s="9">
         <f t="shared" ref="M10:M16" si="2">L10*J10</f>
-        <v>9.0200000000000014</v>
-      </c>
-      <c r="N10" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="N10" s="39">
         <f>L10+L11+L12+L13+L14+L15+L16</f>
-        <v>50.338000000000008</v>
-      </c>
-      <c r="O10" s="42">
+        <v>3.5</v>
+      </c>
+      <c r="O10" s="46">
         <v>4</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -1314,15 +1303,15 @@
       </c>
       <c r="T10" s="1">
         <f>MAX($I$3,($E$3*S10-$A$6)+(($E$3*S10*$C$6-$A$6)-($E$3*S10-$A$6))*$B$6*R10)</f>
-        <v>9.0200000000000014</v>
+        <v>0.5</v>
       </c>
       <c r="U10" s="1">
         <f>T10*R10</f>
-        <v>9.0200000000000014</v>
-      </c>
-      <c r="V10" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="V10" s="43">
         <f>T10+T11+T12</f>
-        <v>34.840000000000003</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.15">
@@ -1337,14 +1326,14 @@
       </c>
       <c r="D11" s="1">
         <f>MAX($I$3,($E$3*C11-$A$6)+(($E$3*C11*$C$6-$A$6)-($E$3*C11-$A$6))*$B$6*B11)</f>
-        <v>9.0200000000000014</v>
+        <v>0.5</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" si="0"/>
-        <v>9.0200000000000014</v>
-      </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="42"/>
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="40"/>
+      <c r="G11" s="46"/>
       <c r="I11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1356,14 +1345,14 @@
       </c>
       <c r="L11" s="1">
         <f t="shared" si="1"/>
-        <v>9.0200000000000014</v>
+        <v>0.5</v>
       </c>
       <c r="M11" s="9">
         <f t="shared" si="2"/>
-        <v>9.0200000000000014</v>
-      </c>
-      <c r="N11" s="46"/>
-      <c r="O11" s="42"/>
+        <v>0.5</v>
+      </c>
+      <c r="N11" s="40"/>
+      <c r="O11" s="46"/>
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1375,13 +1364,13 @@
       </c>
       <c r="T11" s="1">
         <f>MAX($I$3,($E$3*S11-$A$6)+(($E$3*S11*$C$6-$A$6)-($E$3*S11-$A$6))*$B$6*R11)</f>
-        <v>9.0200000000000014</v>
+        <v>0.5</v>
       </c>
       <c r="U11" s="1">
         <f>T11*R11</f>
-        <v>9.0200000000000014</v>
-      </c>
-      <c r="V11" s="40"/>
+        <v>0.5</v>
+      </c>
+      <c r="V11" s="44"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
@@ -1395,14 +1384,14 @@
       </c>
       <c r="D12" s="1">
         <f>MAX($I$3,($E$3*C12-$A$6)+(($E$3*C12*$C$6-$A$6)-($E$3*C12-$A$6))*$B$6*B12)</f>
-        <v>9.24</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="0"/>
-        <v>18.48</v>
-      </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="42"/>
+        <v>1</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="46"/>
       <c r="I12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1414,14 +1403,14 @@
       </c>
       <c r="L12" s="1">
         <f t="shared" si="1"/>
-        <v>9.24</v>
+        <v>0.5</v>
       </c>
       <c r="M12" s="9">
         <f t="shared" si="2"/>
-        <v>18.48</v>
-      </c>
-      <c r="N12" s="46"/>
-      <c r="O12" s="42"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="40"/>
+      <c r="O12" s="46"/>
       <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
@@ -1433,13 +1422,13 @@
       </c>
       <c r="T12" s="1">
         <f>MAX($I$3,($E$3*S12-$A$6)+(($E$3*S12*$C$6-$A$6)-($E$3*S12-$A$6))*$B$6*R12)</f>
-        <v>16.8</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="U12" s="1">
         <f>T12*R12</f>
-        <v>33.6</v>
-      </c>
-      <c r="V12" s="41"/>
+        <v>1.6800000000000002</v>
+      </c>
+      <c r="V12" s="45"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -1453,14 +1442,14 @@
       </c>
       <c r="D13" s="1">
         <f>MAX($I$3,($E$3*C13-$A$6)+(($E$3*C13*$C$6-$A$6)-($E$3*C13-$A$6))*$B$6*B13)</f>
-        <v>9.24</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="0"/>
-        <v>18.48</v>
-      </c>
-      <c r="F13" s="44"/>
-      <c r="G13" s="42"/>
+        <v>1</v>
+      </c>
+      <c r="F13" s="41"/>
+      <c r="G13" s="46"/>
       <c r="I13" s="1" t="s">
         <v>23</v>
       </c>
@@ -1472,14 +1461,14 @@
       </c>
       <c r="L13" s="1">
         <f t="shared" si="1"/>
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="M13" s="9">
         <f t="shared" si="2"/>
-        <v>61</v>
-      </c>
-      <c r="N13" s="46"/>
-      <c r="O13" s="42"/>
+        <v>5</v>
+      </c>
+      <c r="N13" s="40"/>
+      <c r="O13" s="46"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
@@ -1493,17 +1482,17 @@
       </c>
       <c r="D14" s="1">
         <f>MAX($I$3,($E$3*C14-$A$6)+(($E$3*C14*$C$6-$A$6)-($E$3*C14-$A$6))*$B$6*B14)</f>
-        <v>15.75</v>
+        <v>0.78749999999999998</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="0"/>
-        <v>31.5</v>
-      </c>
-      <c r="F14" s="43">
+        <v>1.575</v>
+      </c>
+      <c r="F14" s="39">
         <f>D10+D11+D12+D14+D15</f>
-        <v>59.155000000000001</v>
-      </c>
-      <c r="G14" s="42">
+        <v>3.09375</v>
+      </c>
+      <c r="G14" s="46">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -1517,14 +1506,14 @@
       </c>
       <c r="L14" s="1">
         <f t="shared" si="1"/>
-        <v>5.734</v>
+        <v>0.5</v>
       </c>
       <c r="M14" s="9">
         <f t="shared" si="2"/>
-        <v>40.137999999999998</v>
-      </c>
-      <c r="N14" s="46"/>
-      <c r="O14" s="42"/>
+        <v>3.5</v>
+      </c>
+      <c r="N14" s="40"/>
+      <c r="O14" s="46"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
@@ -1538,14 +1527,14 @@
       </c>
       <c r="D15" s="1">
         <f>MAX($I$3,($E$3*C15-$A$6)+(($E$3*C15*$C$6-$A$6)-($E$3*C15-$A$6))*$B$6*B15)</f>
-        <v>16.125</v>
+        <v>0.80625000000000002</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="0"/>
-        <v>48.375</v>
-      </c>
-      <c r="F15" s="44"/>
-      <c r="G15" s="42"/>
+        <v>2.4187500000000002</v>
+      </c>
+      <c r="F15" s="41"/>
+      <c r="G15" s="46"/>
       <c r="I15" s="1" t="s">
         <v>27</v>
       </c>
@@ -1557,14 +1546,14 @@
       </c>
       <c r="L15" s="1">
         <f t="shared" si="1"/>
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="M15" s="9">
         <f t="shared" si="2"/>
-        <v>61</v>
-      </c>
-      <c r="N15" s="46"/>
-      <c r="O15" s="42"/>
+        <v>5</v>
+      </c>
+      <c r="N15" s="40"/>
+      <c r="O15" s="46"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="D16" s="6" t="s">
@@ -1572,11 +1561,11 @@
       </c>
       <c r="E16" s="10">
         <f>SUM(E10:E13)</f>
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="F16" s="11">
         <f>E16/G10</f>
-        <v>36.666666666666664</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>28</v>
@@ -1589,14 +1578,14 @@
       </c>
       <c r="L16" s="1">
         <f t="shared" si="1"/>
-        <v>5.1239999999999997</v>
+        <v>0.5</v>
       </c>
       <c r="M16" s="9">
         <f t="shared" si="2"/>
-        <v>10.247999999999999</v>
-      </c>
-      <c r="N16" s="44"/>
-      <c r="O16" s="42"/>
+        <v>1</v>
+      </c>
+      <c r="N16" s="41"/>
+      <c r="O16" s="46"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D17" s="6" t="s">
@@ -1604,11 +1593,11 @@
       </c>
       <c r="E17" s="10">
         <f>SUM(E10:E15)</f>
-        <v>134.875</v>
+        <v>6.9937500000000004</v>
       </c>
       <c r="F17" s="11">
         <f>E17/G14</f>
-        <v>44.958333333333336</v>
+        <v>2.3312500000000003</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="5"/>
@@ -1618,11 +1607,11 @@
       </c>
       <c r="M17" s="10">
         <f>SUM(M10:M16)</f>
-        <v>208.90600000000001</v>
+        <v>16.5</v>
       </c>
       <c r="N17" s="10">
         <f>M17/O10</f>
-        <v>52.226500000000001</v>
+        <v>4.125</v>
       </c>
       <c r="O17" s="5"/>
     </row>
@@ -1710,11 +1699,11 @@
       </c>
       <c r="D22" s="1">
         <f>MAX($I$3,($E$3*C22-$A$6)+(($E$3*C22*$C$6-$A$6)-($E$3*C22-$A$6))*$B$6*B22)</f>
-        <v>10.25</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="E22" s="1">
         <f>D22*B22</f>
-        <v>10.25</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>18</v>
@@ -1732,7 +1721,7 @@
         <f t="shared" ref="M22:M26" si="3">L22*J22</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N22" s="39">
+      <c r="N22" s="43">
         <f>L22+L23+L24</f>
         <v>0.84000000000000008</v>
       </c>
@@ -1750,11 +1739,11 @@
       </c>
       <c r="D23" s="1">
         <f>MAX($I$3,($E$3*C23-$A$6)+(($E$3*C23*$C$6-$A$6)-($E$3*C23-$A$6))*$B$6*B23)</f>
-        <v>9.4600000000000009</v>
+        <v>0.5</v>
       </c>
       <c r="E23" s="1">
         <f>D23*B23</f>
-        <v>28.380000000000003</v>
+        <v>1.5</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>19</v>
@@ -1772,7 +1761,7 @@
         <f t="shared" si="3"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N23" s="40"/>
+      <c r="N23" s="44"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
@@ -1787,11 +1776,11 @@
       </c>
       <c r="D24" s="1">
         <f>MAX($I$3,($E$3*C24-$A$6)+(($E$3*C24*$C$6-$A$6)-($E$3*C24-$A$6))*$B$6*B24)</f>
-        <v>12.6</v>
+        <v>0.63</v>
       </c>
       <c r="E24" s="1">
         <f>D24*B24</f>
-        <v>25.2</v>
+        <v>1.26</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>20</v>
@@ -1809,7 +1798,7 @@
         <f t="shared" si="3"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N24" s="41"/>
+      <c r="N24" s="45"/>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.15">
@@ -1824,11 +1813,11 @@
       </c>
       <c r="D25" s="1">
         <f>MAX($I$3,($E$3*C25-$A$6)+(($E$3*C25*$C$6-$A$6)-($E$3*C25-$A$6))*$B$6*B25)</f>
-        <v>9.24</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="1">
         <f>D25*B25</f>
-        <v>18.48</v>
+        <v>1</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>23</v>
@@ -1846,7 +1835,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N25" s="39">
+      <c r="N25" s="43">
         <f>L22+L23+L25+L26</f>
         <v>1.2400000000000002</v>
       </c>
@@ -1869,7 +1858,7 @@
         <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
-      <c r="N26" s="41"/>
+      <c r="N26" s="45"/>
       <c r="O26" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
@@ -1883,7 +1872,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="47" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="37"/>
@@ -1892,7 +1881,7 @@
       <c r="E30" s="37"/>
       <c r="F30" s="38"/>
       <c r="G30" s="4"/>
-      <c r="I30" s="45" t="s">
+      <c r="I30" s="47" t="s">
         <v>44</v>
       </c>
       <c r="J30" s="37"/>
@@ -1958,17 +1947,17 @@
       </c>
       <c r="D32" s="1">
         <f>MAX($I$3,($E$3*C32-$A$6)+(($E$3*C32*$C$6-$A$6)-($E$3*C32-$A$6))*$B$6)</f>
-        <v>14.145</v>
+        <v>0.70724999999999993</v>
       </c>
       <c r="E32" s="9">
         <f t="shared" ref="E32:E37" si="4">D32*B32</f>
-        <v>14.145</v>
-      </c>
-      <c r="F32" s="43">
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="F32" s="39">
         <f>D32+D33+D34+D35</f>
-        <v>57.269999999999996</v>
-      </c>
-      <c r="G32" s="42">
+        <v>2.8634999999999997</v>
+      </c>
+      <c r="G32" s="46">
         <v>1.5</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -1982,17 +1971,17 @@
       </c>
       <c r="L32" s="1">
         <f t="shared" ref="L32:L38" si="5">MAX($I$3,($E$3*K32-$A$6)+(($E$3*K32*$C$6-$A$6)-($E$3*K32-$A$6))*$B$6*J32)</f>
-        <v>14.145</v>
+        <v>0.70724999999999993</v>
       </c>
       <c r="M32" s="9">
         <f t="shared" ref="M32:M38" si="6">L32*J32</f>
-        <v>14.145</v>
-      </c>
-      <c r="N32" s="43">
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="N32" s="39">
         <f>L32+L33+L34+L35+L36+L37+L38</f>
-        <v>89.46299999999998</v>
-      </c>
-      <c r="O32" s="42">
+        <v>4.4731499999999995</v>
+      </c>
+      <c r="O32" s="46">
         <v>4</v>
       </c>
     </row>
@@ -2008,14 +1997,14 @@
       </c>
       <c r="D33" s="1">
         <f>MAX($I$3,($E$3*C33-$A$6)+(($E$3*C33*$C$6-$A$6)-($E$3*C33-$A$6))*$B$6*B33)</f>
-        <v>14.145</v>
+        <v>0.70724999999999993</v>
       </c>
       <c r="E33" s="9">
         <f t="shared" si="4"/>
-        <v>14.145</v>
-      </c>
-      <c r="F33" s="46"/>
-      <c r="G33" s="42"/>
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="F33" s="40"/>
+      <c r="G33" s="46"/>
       <c r="I33" s="1" t="s">
         <v>19</v>
       </c>
@@ -2027,14 +2016,14 @@
       </c>
       <c r="L33" s="1">
         <f t="shared" si="5"/>
-        <v>14.145</v>
+        <v>0.70724999999999993</v>
       </c>
       <c r="M33" s="9">
         <f t="shared" si="6"/>
-        <v>14.145</v>
-      </c>
-      <c r="N33" s="46"/>
-      <c r="O33" s="42"/>
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="N33" s="40"/>
+      <c r="O33" s="46"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
@@ -2048,14 +2037,14 @@
       </c>
       <c r="D34" s="1">
         <f>MAX($I$3,($E$3*C34-$A$6)+(($E$3*C34*$C$6-$A$6)-($E$3*C34-$A$6))*$B$6*B34)</f>
-        <v>14.489999999999998</v>
+        <v>0.72449999999999992</v>
       </c>
       <c r="E34" s="9">
         <f t="shared" si="4"/>
-        <v>28.979999999999997</v>
-      </c>
-      <c r="F34" s="46"/>
-      <c r="G34" s="42"/>
+        <v>1.4489999999999998</v>
+      </c>
+      <c r="F34" s="40"/>
+      <c r="G34" s="46"/>
       <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
@@ -2067,14 +2056,14 @@
       </c>
       <c r="L34" s="1">
         <f t="shared" si="5"/>
-        <v>14.489999999999998</v>
+        <v>0.72449999999999992</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" si="6"/>
-        <v>28.979999999999997</v>
-      </c>
-      <c r="N34" s="46"/>
-      <c r="O34" s="42"/>
+        <v>1.4489999999999998</v>
+      </c>
+      <c r="N34" s="40"/>
+      <c r="O34" s="46"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
@@ -2088,14 +2077,14 @@
       </c>
       <c r="D35" s="1">
         <f>MAX($I$3,($E$3*C35-$A$6)+(($E$3*C35*$C$6-$A$6)-($E$3*C35-$A$6))*$B$6*B35)</f>
-        <v>14.489999999999998</v>
+        <v>0.72449999999999992</v>
       </c>
       <c r="E35" s="9">
         <f t="shared" si="4"/>
-        <v>28.979999999999997</v>
-      </c>
-      <c r="F35" s="44"/>
-      <c r="G35" s="42"/>
+        <v>1.4489999999999998</v>
+      </c>
+      <c r="F35" s="41"/>
+      <c r="G35" s="46"/>
       <c r="I35" s="1" t="s">
         <v>23</v>
       </c>
@@ -2107,14 +2096,14 @@
       </c>
       <c r="L35" s="1">
         <f t="shared" si="5"/>
-        <v>12.349999999999998</v>
+        <v>0.61749999999999994</v>
       </c>
       <c r="M35" s="9">
         <f t="shared" si="6"/>
-        <v>123.49999999999997</v>
-      </c>
-      <c r="N35" s="46"/>
-      <c r="O35" s="42"/>
+        <v>6.1749999999999989</v>
+      </c>
+      <c r="N35" s="40"/>
+      <c r="O35" s="46"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -2128,17 +2117,17 @@
       </c>
       <c r="D36" s="1">
         <f>MAX($I$3,($E$3*C36-$A$6)+(($E$3*C36*$C$6-$A$6)-($E$3*C36-$A$6))*$B$6*B36)</f>
-        <v>21</v>
+        <v>1.05</v>
       </c>
       <c r="E36" s="9">
         <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="F36" s="43">
+        <v>2.1</v>
+      </c>
+      <c r="F36" s="39">
         <f>D32+D33+D34+D36+D37</f>
-        <v>85.28</v>
-      </c>
-      <c r="G36" s="42">
+        <v>4.2640000000000002</v>
+      </c>
+      <c r="G36" s="46">
         <v>3</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -2152,14 +2141,14 @@
       </c>
       <c r="L36" s="1">
         <f t="shared" si="5"/>
-        <v>11.608999999999998</v>
+        <v>0.58045000000000002</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="6"/>
-        <v>81.262999999999991</v>
-      </c>
-      <c r="N36" s="46"/>
-      <c r="O36" s="42"/>
+        <v>4.0631500000000003</v>
+      </c>
+      <c r="N36" s="40"/>
+      <c r="O36" s="46"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
@@ -2173,14 +2162,14 @@
       </c>
       <c r="D37" s="1">
         <f>MAX($I$3,($E$3*C37-$A$6)+(($E$3*C37*$C$6-$A$6)-($E$3*C37-$A$6))*$B$6*B37)</f>
-        <v>21.5</v>
+        <v>1.075</v>
       </c>
       <c r="E37" s="9">
         <f t="shared" si="4"/>
-        <v>64.5</v>
-      </c>
-      <c r="F37" s="44"/>
-      <c r="G37" s="42"/>
+        <v>3.2249999999999996</v>
+      </c>
+      <c r="F37" s="41"/>
+      <c r="G37" s="46"/>
       <c r="I37" s="1" t="s">
         <v>27</v>
       </c>
@@ -2192,14 +2181,14 @@
       </c>
       <c r="L37" s="1">
         <f t="shared" si="5"/>
-        <v>12.349999999999998</v>
+        <v>0.61749999999999994</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="6"/>
-        <v>123.49999999999997</v>
-      </c>
-      <c r="N37" s="46"/>
-      <c r="O37" s="42"/>
+        <v>6.1749999999999989</v>
+      </c>
+      <c r="N37" s="40"/>
+      <c r="O37" s="46"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D38" s="6" t="s">
@@ -2207,11 +2196,11 @@
       </c>
       <c r="E38" s="10">
         <f>SUM(E32:E35)</f>
-        <v>86.25</v>
+        <v>4.3125</v>
       </c>
       <c r="F38" s="11">
         <f>E38/G32</f>
-        <v>57.5</v>
+        <v>2.875</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>28</v>
@@ -2224,14 +2213,14 @@
       </c>
       <c r="L38" s="1">
         <f t="shared" si="5"/>
-        <v>10.373999999999999</v>
+        <v>0.51869999999999994</v>
       </c>
       <c r="M38" s="9">
         <f t="shared" si="6"/>
-        <v>20.747999999999998</v>
-      </c>
-      <c r="N38" s="44"/>
-      <c r="O38" s="42"/>
+        <v>1.0373999999999999</v>
+      </c>
+      <c r="N38" s="41"/>
+      <c r="O38" s="46"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="D39" s="6" t="s">
@@ -2239,11 +2228,11 @@
       </c>
       <c r="E39" s="10">
         <f>SUM(E32:E37)</f>
-        <v>192.75</v>
+        <v>9.6374999999999993</v>
       </c>
       <c r="F39" s="11">
         <f>E39/G36</f>
-        <v>64.25</v>
+        <v>3.2124999999999999</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="5"/>
@@ -2253,11 +2242,11 @@
       </c>
       <c r="M39" s="10">
         <f>SUM(M32:M38)</f>
-        <v>406.28099999999989</v>
+        <v>20.314049999999995</v>
       </c>
       <c r="N39" s="10">
         <f>M39/O32</f>
-        <v>101.57024999999997</v>
+        <v>5.0785124999999987</v>
       </c>
       <c r="O39" s="5"/>
     </row>
@@ -2339,11 +2328,11 @@
       </c>
       <c r="D45" s="1">
         <f>MAX($I$3,($E$3*C45-$A$6)+(($E$3*C45*$C$6-$A$6)-($E$3*C45-$A$6))*$B$6*B45)</f>
-        <v>15.375</v>
+        <v>0.76875000000000004</v>
       </c>
       <c r="E45" s="1">
         <f>D45*B45</f>
-        <v>15.375</v>
+        <v>0.76875000000000004</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>18</v>
@@ -2361,7 +2350,7 @@
         <f t="shared" ref="M45:M49" si="7">L45*J45</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N45" s="39">
+      <c r="N45" s="43">
         <f>L45+L46+L47</f>
         <v>0.84000000000000008</v>
       </c>
@@ -2378,11 +2367,11 @@
       </c>
       <c r="D46" s="1">
         <f>MAX($I$3,($E$3*C46-$A$6)+(($E$3*C46*$C$6-$A$6)-($E$3*C46-$A$6))*$B$6*B46)</f>
-        <v>14.834999999999999</v>
+        <v>0.74174999999999991</v>
       </c>
       <c r="E46" s="1">
         <f>D46*B46</f>
-        <v>44.504999999999995</v>
+        <v>2.22525</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>19</v>
@@ -2400,7 +2389,7 @@
         <f t="shared" si="7"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="N46" s="40"/>
+      <c r="N46" s="44"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
@@ -2414,11 +2403,11 @@
       </c>
       <c r="D47" s="1">
         <f>MAX($I$3,($E$3*C47-$A$6)+(($E$3*C47*$C$6-$A$6)-($E$3*C47-$A$6))*$B$6*B47)</f>
-        <v>17.850000000000001</v>
+        <v>0.89249999999999996</v>
       </c>
       <c r="E47" s="1">
         <f>D47*B47</f>
-        <v>35.700000000000003</v>
+        <v>1.7849999999999999</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>20</v>
@@ -2436,7 +2425,7 @@
         <f t="shared" si="7"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="N47" s="41"/>
+      <c r="N47" s="45"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
@@ -2450,11 +2439,11 @@
       </c>
       <c r="D48" s="1">
         <f>MAX($I$3,($E$3*C48-$A$6)+(($E$3*C48*$C$6-$A$6)-($E$3*C48-$A$6))*$B$6*B48)</f>
-        <v>14.489999999999998</v>
+        <v>0.72449999999999992</v>
       </c>
       <c r="E48" s="1">
         <f>D48*B48</f>
-        <v>28.979999999999997</v>
+        <v>1.4489999999999998</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>23</v>
@@ -2472,7 +2461,7 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N48" s="39">
+      <c r="N48" s="43">
         <f>L45+L46+L48+L49</f>
         <v>1.2400000000000002</v>
       </c>
@@ -2494,10 +2483,29 @@
         <f t="shared" si="7"/>
         <v>0.68</v>
       </c>
-      <c r="N49" s="41"/>
+      <c r="N49" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="I20:N20"/>
     <mergeCell ref="F10:F13"/>
@@ -2507,44 +2515,14 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="Q8:V8"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:AZ21"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2594,57 +2572,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="50"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="48" t="s">
+      <c r="V3" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="48"/>
-      <c r="X3" s="48"/>
-      <c r="Y3" s="48"/>
-      <c r="Z3" s="48"/>
-      <c r="AA3" s="48"/>
-      <c r="AB3" s="48"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="48"/>
-      <c r="AF3" s="48"/>
-      <c r="AG3" s="48"/>
-      <c r="AH3" s="48"/>
-      <c r="AI3" s="48"/>
-      <c r="AJ3" s="48"/>
-      <c r="AK3" s="48"/>
-      <c r="AL3" s="48"/>
-      <c r="AM3" s="48"/>
-      <c r="AN3" s="48"/>
-      <c r="AO3" s="48"/>
-      <c r="AP3" s="48"/>
-      <c r="AQ3" s="48"/>
-      <c r="AR3" s="48"/>
-      <c r="AS3" s="48"/>
-      <c r="AT3" s="48"/>
-      <c r="AU3" s="48"/>
-      <c r="AV3" s="48"/>
-      <c r="AW3" s="48"/>
-      <c r="AX3" s="48"/>
-      <c r="AY3" s="48"/>
+      <c r="W3" s="50"/>
+      <c r="X3" s="50"/>
+      <c r="Y3" s="50"/>
+      <c r="Z3" s="50"/>
+      <c r="AA3" s="50"/>
+      <c r="AB3" s="50"/>
+      <c r="AC3" s="50"/>
+      <c r="AD3" s="50"/>
+      <c r="AE3" s="50"/>
+      <c r="AF3" s="50"/>
+      <c r="AG3" s="50"/>
+      <c r="AH3" s="50"/>
+      <c r="AI3" s="50"/>
+      <c r="AJ3" s="50"/>
+      <c r="AK3" s="50"/>
+      <c r="AL3" s="50"/>
+      <c r="AM3" s="50"/>
+      <c r="AN3" s="50"/>
+      <c r="AO3" s="50"/>
+      <c r="AP3" s="50"/>
+      <c r="AQ3" s="50"/>
+      <c r="AR3" s="50"/>
+      <c r="AS3" s="50"/>
+      <c r="AT3" s="50"/>
+      <c r="AU3" s="50"/>
+      <c r="AV3" s="50"/>
+      <c r="AW3" s="50"/>
+      <c r="AX3" s="50"/>
+      <c r="AY3" s="50"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2690,44 +2668,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="49" t="s">
+      <c r="V4" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="49"/>
-      <c r="X4" s="49"/>
-      <c r="Y4" s="49"/>
-      <c r="Z4" s="49"/>
-      <c r="AA4" s="49"/>
+      <c r="W4" s="51"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="49" t="s">
+      <c r="AD4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="49"/>
-      <c r="AF4" s="49"/>
-      <c r="AG4" s="49"/>
+      <c r="AE4" s="51"/>
+      <c r="AF4" s="51"/>
+      <c r="AG4" s="51"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="49" t="s">
+      <c r="AL4" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="49"/>
-      <c r="AN4" s="49"/>
-      <c r="AO4" s="49"/>
-      <c r="AP4" s="49"/>
-      <c r="AQ4" s="49"/>
+      <c r="AM4" s="51"/>
+      <c r="AN4" s="51"/>
+      <c r="AO4" s="51"/>
+      <c r="AP4" s="51"/>
+      <c r="AQ4" s="51"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="49" t="s">
+      <c r="AT4" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="49"/>
-      <c r="AV4" s="49"/>
-      <c r="AW4" s="49"/>
-      <c r="AX4" s="49"/>
-      <c r="AY4" s="49"/>
+      <c r="AU4" s="51"/>
+      <c r="AV4" s="51"/>
+      <c r="AW4" s="51"/>
+      <c r="AX4" s="51"/>
+      <c r="AY4" s="51"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2869,7 +2847,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="50">
+      <c r="B6" s="48">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -3030,7 +3008,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="50"/>
+      <c r="B7" s="48"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -3189,7 +3167,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="50">
+      <c r="B8" s="48">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -3350,7 +3328,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="50"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -3509,7 +3487,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="51">
+      <c r="B10" s="49">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3670,10 +3648,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="51"/>
+      <c r="B11" s="49"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="51"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3832,7 +3810,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="50">
+      <c r="B13" s="48">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -3993,7 +3971,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="50"/>
+      <c r="B14" s="48"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -4152,7 +4130,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="50">
+      <c r="B16" s="48">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -4313,7 +4291,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="50"/>
+      <c r="B17" s="48"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -4472,7 +4450,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="50"/>
+      <c r="B18" s="48"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4631,7 +4609,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="50">
+      <c r="B20" s="48">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -4792,7 +4770,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="50"/>
+      <c r="B21" s="48"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -4952,21 +4930,32 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="V3:AY3"/>
+    <mergeCell ref="AT4:AY4"/>
+    <mergeCell ref="AL4:AQ4"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="V4:AA4"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B16:B18"/>
-    <mergeCell ref="D3:P3"/>
-    <mergeCell ref="V3:AY3"/>
-    <mergeCell ref="AT4:AY4"/>
-    <mergeCell ref="AL4:AQ4"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="V4:AA4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
 </file>
--- a/dev_docs/千界万锻数值表格-V1.6-2025-10-8.xlsx
+++ b/dev_docs/千界万锻数值表格-V1.6-2025-10-8.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\SDBF\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93322935-1AFA-45C8-9FF3-ABBEEAFAEA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA3364C-58F3-40A9-B2A1-5A3AC47B67C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="普通攻击" sheetId="1" r:id="rId1"/>
-    <sheet name="数值分配" sheetId="3" r:id="rId2"/>
-    <sheet name="技能" sheetId="2" r:id="rId3"/>
+    <sheet name="数值分配" sheetId="3" r:id="rId1"/>
+    <sheet name="维度" sheetId="4" r:id="rId2"/>
+    <sheet name="普通攻击" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="200">
   <si>
     <t>最终攻击力=面板攻击+横扫之刃+评分等级+杀手附魔</t>
   </si>
@@ -354,13 +354,519 @@
   <si>
     <t>100+</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>~2</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0~1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>~3</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>~4</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>廉价材料</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通材料</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有材料</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>突破材料</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>豆腐</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>深1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>天境</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>月球</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>下界</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>火星</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>金星</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>水星</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>深3（午夜）</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>深2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>深园</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>末地</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>小行星</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>土星</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄蜂</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>土星环</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>末地里</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>冥王星</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜原星</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>深4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>主世界上</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>主世界下</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2~3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3~4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>4~5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>神能晶</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>戴斯</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔幻冰</t>
+  </si>
+  <si>
+    <t>运算处理器</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>合金碎片</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>凋零头</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘碱晶</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐热金属</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>御腐水晶</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>厄瑟锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>末地钢</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑导向零件</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>钍锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>锂锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>镁锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇异物质尘</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰坦II复合锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>古代灵魂</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚金</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>不融冰</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾普塞隆尘</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>虹移之熵</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>待定</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>末影锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>双层电容</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>空散热器</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> NA</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>维度</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>难度分级</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段划分</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈焰棒</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫金</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>暮色（牛头雪怪后）</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>暮色（骑士前）</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛头人肉</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魂泪</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>砷铅铁</t>
+  </si>
+  <si>
+    <t>极地毛坯</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫磺块</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>远古金属粒</t>
+  </si>
+  <si>
+    <t>骸龙之骨</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>远古金属锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>墨丘利组件</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔豆</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜冥锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>腐化珍珠</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑暗珍珠</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>幽光</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>黯铁</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜钢</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵豪</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗忆锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫菘结晶</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>风暴精华</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>德尔塔尘</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>星空循环组件</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>红石蜜蜂网</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>多面蜜酒</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ML计算锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔法尘</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>混沌真理</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇点合金</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>辐射零件组</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁木锭</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>天晶混合</t>
+  </si>
+  <si>
+    <t>金</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MS3C</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,8 +913,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,8 +1025,92 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6C3FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CEB99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -621,13 +1225,99 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -745,31 +1435,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -778,20 +1474,203 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" xfId="6" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="8" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="1" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="1" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="9">
+    <cellStyle name="20% - 着色 3" xfId="3" builtinId="38"/>
+    <cellStyle name="20% - 着色 4" xfId="5" builtinId="42"/>
+    <cellStyle name="20% - 着色 6" xfId="7" builtinId="50"/>
+    <cellStyle name="40% - 着色 1" xfId="1" builtinId="31"/>
+    <cellStyle name="40% - 着色 3" xfId="4" builtinId="39"/>
+    <cellStyle name="40% - 着色 4" xfId="6" builtinId="43"/>
+    <cellStyle name="40% - 着色 6" xfId="8" builtinId="51"/>
+    <cellStyle name="60% - 着色 1" xfId="2" builtinId="32"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFCCFF"/>
       <color rgb="FFFDEEE3"/>
     </mruColors>
   </colors>
@@ -1055,1474 +1934,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="5" max="5" width="10.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="G1" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9">
-        <f>A3+B3+(C3/2)+D3</f>
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
-        <v>0</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A8" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="4"/>
-      <c r="I8" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="1"/>
-      <c r="Q8" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="38"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="D10" s="1">
-        <f>MAX($I$3,($E$3*C10-$A$6)+(($E$3*C10*$C$6-$A$6)-($E$3*C10-$A$6))*$B$6)</f>
-        <v>0.5</v>
-      </c>
-      <c r="E10" s="9">
-        <f t="shared" ref="E10:E15" si="0">D10*B10</f>
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="39">
-        <f>D10+D11+D12+D13</f>
-        <v>2</v>
-      </c>
-      <c r="G10" s="46">
-        <v>1.5</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="L10" s="1">
-        <f t="shared" ref="L10:L16" si="1">MAX($I$3,($E$3*K10-$A$6)+(($E$3*K10*$C$6-$A$6)-($E$3*K10-$A$6))*$B$6*J10)</f>
-        <v>0.5</v>
-      </c>
-      <c r="M10" s="9">
-        <f t="shared" ref="M10:M16" si="2">L10*J10</f>
-        <v>0.5</v>
-      </c>
-      <c r="N10" s="39">
-        <f>L10+L11+L12+L13+L14+L15+L16</f>
-        <v>3.5</v>
-      </c>
-      <c r="O10" s="46">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R10" s="1">
-        <v>1</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="T10" s="1">
-        <f>MAX($I$3,($E$3*S10-$A$6)+(($E$3*S10*$C$6-$A$6)-($E$3*S10-$A$6))*$B$6*R10)</f>
-        <v>0.5</v>
-      </c>
-      <c r="U10" s="1">
-        <f>T10*R10</f>
-        <v>0.5</v>
-      </c>
-      <c r="V10" s="43">
-        <f>T10+T11+T12</f>
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="D11" s="1">
-        <f>MAX($I$3,($E$3*C11-$A$6)+(($E$3*C11*$C$6-$A$6)-($E$3*C11-$A$6))*$B$6*B11)</f>
-        <v>0.5</v>
-      </c>
-      <c r="E11" s="9">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="46"/>
-      <c r="I11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="L11" s="1">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="M11" s="9">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="N11" s="40"/>
-      <c r="O11" s="46"/>
-      <c r="Q11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R11" s="1">
-        <v>1</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="T11" s="1">
-        <f>MAX($I$3,($E$3*S11-$A$6)+(($E$3*S11*$C$6-$A$6)-($E$3*S11-$A$6))*$B$6*R11)</f>
-        <v>0.5</v>
-      </c>
-      <c r="U11" s="1">
-        <f>T11*R11</f>
-        <v>0.5</v>
-      </c>
-      <c r="V11" s="44"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="D12" s="1">
-        <f>MAX($I$3,($E$3*C12-$A$6)+(($E$3*C12*$C$6-$A$6)-($E$3*C12-$A$6))*$B$6*B12)</f>
-        <v>0.5</v>
-      </c>
-      <c r="E12" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="46"/>
-      <c r="I12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="1">
-        <v>2</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="L12" s="1">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="M12" s="9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N12" s="40"/>
-      <c r="O12" s="46"/>
-      <c r="Q12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R12" s="1">
-        <v>2</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="T12" s="1">
-        <f>MAX($I$3,($E$3*S12-$A$6)+(($E$3*S12*$C$6-$A$6)-($E$3*S12-$A$6))*$B$6*R12)</f>
-        <v>0.84000000000000008</v>
-      </c>
-      <c r="U12" s="1">
-        <f>T12*R12</f>
-        <v>1.6800000000000002</v>
-      </c>
-      <c r="V12" s="45"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="D13" s="1">
-        <f>MAX($I$3,($E$3*C13-$A$6)+(($E$3*C13*$C$6-$A$6)-($E$3*C13-$A$6))*$B$6*B13)</f>
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F13" s="41"/>
-      <c r="G13" s="46"/>
-      <c r="I13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" s="1">
-        <v>10</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="L13" s="1">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="M13" s="9">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="N13" s="40"/>
-      <c r="O13" s="46"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="D14" s="1">
-        <f>MAX($I$3,($E$3*C14-$A$6)+(($E$3*C14*$C$6-$A$6)-($E$3*C14-$A$6))*$B$6*B14)</f>
-        <v>0.78749999999999998</v>
-      </c>
-      <c r="E14" s="9">
-        <f t="shared" si="0"/>
-        <v>1.575</v>
-      </c>
-      <c r="F14" s="39">
-        <f>D10+D11+D12+D14+D15</f>
-        <v>3.09375</v>
-      </c>
-      <c r="G14" s="46">
-        <v>3</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="1">
-        <v>7</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="L14" s="1">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="M14" s="9">
-        <f t="shared" si="2"/>
-        <v>3.5</v>
-      </c>
-      <c r="N14" s="40"/>
-      <c r="O14" s="46"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="1">
-        <v>3</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="D15" s="1">
-        <f>MAX($I$3,($E$3*C15-$A$6)+(($E$3*C15*$C$6-$A$6)-($E$3*C15-$A$6))*$B$6*B15)</f>
-        <v>0.80625000000000002</v>
-      </c>
-      <c r="E15" s="9">
-        <f t="shared" si="0"/>
-        <v>2.4187500000000002</v>
-      </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="46"/>
-      <c r="I15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="1">
-        <v>10</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="L15" s="1">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="M15" s="9">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="N15" s="40"/>
-      <c r="O15" s="46"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="D16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="10">
-        <f>SUM(E10:E13)</f>
-        <v>3</v>
-      </c>
-      <c r="F16" s="11">
-        <f>E16/G10</f>
-        <v>2</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="1">
-        <v>2</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="L16" s="1">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="M16" s="9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N16" s="41"/>
-      <c r="O16" s="46"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="D17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="10">
-        <f>SUM(E10:E15)</f>
-        <v>6.9937500000000004</v>
-      </c>
-      <c r="F17" s="11">
-        <f>E17/G14</f>
-        <v>2.3312500000000003</v>
-      </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M17" s="10">
-        <f>SUM(M10:M16)</f>
-        <v>16.5</v>
-      </c>
-      <c r="N17" s="10">
-        <f>M17/O10</f>
-        <v>4.125</v>
-      </c>
-      <c r="O17" s="5"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="E18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A20" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="I20" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="5"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O21" s="5"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="D22" s="1">
-        <f>MAX($I$3,($E$3*C22-$A$6)+(($E$3*C22*$C$6-$A$6)-($E$3*C22-$A$6))*$B$6*B22)</f>
-        <v>0.51249999999999996</v>
-      </c>
-      <c r="E22" s="1">
-        <f>D22*B22</f>
-        <v>0.51249999999999996</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="M22" s="1">
-        <f t="shared" ref="M22:M26" si="3">L22*J22</f>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N22" s="43">
-        <f>L22+L23+L24</f>
-        <v>0.84000000000000008</v>
-      </c>
-      <c r="O22" s="5"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="1">
-        <v>3</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="D23" s="1">
-        <f>MAX($I$3,($E$3*C23-$A$6)+(($E$3*C23*$C$6-$A$6)-($E$3*C23-$A$6))*$B$6*B23)</f>
-        <v>0.5</v>
-      </c>
-      <c r="E23" s="1">
-        <f>D23*B23</f>
-        <v>1.5</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="M23" s="1">
-        <f t="shared" si="3"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N23" s="44"/>
-      <c r="O23" s="5"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D24" s="1">
-        <f>MAX($I$3,($E$3*C24-$A$6)+(($E$3*C24*$C$6-$A$6)-($E$3*C24-$A$6))*$B$6*B24)</f>
-        <v>0.63</v>
-      </c>
-      <c r="E24" s="1">
-        <f>D24*B24</f>
-        <v>1.26</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="1">
-        <v>2</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="M24" s="1">
-        <f t="shared" si="3"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="N24" s="45"/>
-      <c r="O24" s="5"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="1">
-        <v>2</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="D25" s="1">
-        <f>MAX($I$3,($E$3*C25-$A$6)+(($E$3*C25*$C$6-$A$6)-($E$3*C25-$A$6))*$B$6*B25)</f>
-        <v>0.5</v>
-      </c>
-      <c r="E25" s="1">
-        <f>D25*B25</f>
-        <v>1</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" s="1">
-        <v>2</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="M25" s="1">
-        <f t="shared" si="3"/>
-        <v>0.68</v>
-      </c>
-      <c r="N25" s="43">
-        <f>L22+L23+L25+L26</f>
-        <v>1.2400000000000002</v>
-      </c>
-      <c r="O25" s="5"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="I26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" s="1">
-        <v>2</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="M26" s="1">
-        <f t="shared" si="3"/>
-        <v>0.68</v>
-      </c>
-      <c r="N26" s="45"/>
-      <c r="O26" s="5"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A29">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="4"/>
-      <c r="I30" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="J30" s="37"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="37"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="D32" s="1">
-        <f>MAX($I$3,($E$3*C32-$A$6)+(($E$3*C32*$C$6-$A$6)-($E$3*C32-$A$6))*$B$6)</f>
-        <v>0.70724999999999993</v>
-      </c>
-      <c r="E32" s="9">
-        <f t="shared" ref="E32:E37" si="4">D32*B32</f>
-        <v>0.70724999999999993</v>
-      </c>
-      <c r="F32" s="39">
-        <f>D32+D33+D34+D35</f>
-        <v>2.8634999999999997</v>
-      </c>
-      <c r="G32" s="46">
-        <v>1.5</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="L32" s="1">
-        <f t="shared" ref="L32:L38" si="5">MAX($I$3,($E$3*K32-$A$6)+(($E$3*K32*$C$6-$A$6)-($E$3*K32-$A$6))*$B$6*J32)</f>
-        <v>0.70724999999999993</v>
-      </c>
-      <c r="M32" s="9">
-        <f t="shared" ref="M32:M38" si="6">L32*J32</f>
-        <v>0.70724999999999993</v>
-      </c>
-      <c r="N32" s="39">
-        <f>L32+L33+L34+L35+L36+L37+L38</f>
-        <v>4.4731499999999995</v>
-      </c>
-      <c r="O32" s="46">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="D33" s="1">
-        <f>MAX($I$3,($E$3*C33-$A$6)+(($E$3*C33*$C$6-$A$6)-($E$3*C33-$A$6))*$B$6*B33)</f>
-        <v>0.70724999999999993</v>
-      </c>
-      <c r="E33" s="9">
-        <f t="shared" si="4"/>
-        <v>0.70724999999999993</v>
-      </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="46"/>
-      <c r="I33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="L33" s="1">
-        <f t="shared" si="5"/>
-        <v>0.70724999999999993</v>
-      </c>
-      <c r="M33" s="9">
-        <f t="shared" si="6"/>
-        <v>0.70724999999999993</v>
-      </c>
-      <c r="N33" s="40"/>
-      <c r="O33" s="46"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="1">
-        <v>2</v>
-      </c>
-      <c r="C34" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="D34" s="1">
-        <f>MAX($I$3,($E$3*C34-$A$6)+(($E$3*C34*$C$6-$A$6)-($E$3*C34-$A$6))*$B$6*B34)</f>
-        <v>0.72449999999999992</v>
-      </c>
-      <c r="E34" s="9">
-        <f t="shared" si="4"/>
-        <v>1.4489999999999998</v>
-      </c>
-      <c r="F34" s="40"/>
-      <c r="G34" s="46"/>
-      <c r="I34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="1">
-        <v>2</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="L34" s="1">
-        <f t="shared" si="5"/>
-        <v>0.72449999999999992</v>
-      </c>
-      <c r="M34" s="9">
-        <f t="shared" si="6"/>
-        <v>1.4489999999999998</v>
-      </c>
-      <c r="N34" s="40"/>
-      <c r="O34" s="46"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="1">
-        <v>2</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="D35" s="1">
-        <f>MAX($I$3,($E$3*C35-$A$6)+(($E$3*C35*$C$6-$A$6)-($E$3*C35-$A$6))*$B$6*B35)</f>
-        <v>0.72449999999999992</v>
-      </c>
-      <c r="E35" s="9">
-        <f t="shared" si="4"/>
-        <v>1.4489999999999998</v>
-      </c>
-      <c r="F35" s="41"/>
-      <c r="G35" s="46"/>
-      <c r="I35" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J35" s="1">
-        <v>10</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0.49399999999999999</v>
-      </c>
-      <c r="L35" s="1">
-        <f t="shared" si="5"/>
-        <v>0.61749999999999994</v>
-      </c>
-      <c r="M35" s="9">
-        <f t="shared" si="6"/>
-        <v>6.1749999999999989</v>
-      </c>
-      <c r="N35" s="40"/>
-      <c r="O35" s="46"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A36" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="1">
-        <v>2</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1</v>
-      </c>
-      <c r="D36" s="1">
-        <f>MAX($I$3,($E$3*C36-$A$6)+(($E$3*C36*$C$6-$A$6)-($E$3*C36-$A$6))*$B$6*B36)</f>
-        <v>1.05</v>
-      </c>
-      <c r="E36" s="9">
-        <f t="shared" si="4"/>
-        <v>2.1</v>
-      </c>
-      <c r="F36" s="39">
-        <f>D32+D33+D34+D36+D37</f>
-        <v>4.2640000000000002</v>
-      </c>
-      <c r="G36" s="46">
-        <v>3</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J36" s="1">
-        <v>7</v>
-      </c>
-      <c r="K36" s="1">
-        <v>0.49399999999999999</v>
-      </c>
-      <c r="L36" s="1">
-        <f t="shared" si="5"/>
-        <v>0.58045000000000002</v>
-      </c>
-      <c r="M36" s="9">
-        <f t="shared" si="6"/>
-        <v>4.0631500000000003</v>
-      </c>
-      <c r="N36" s="40"/>
-      <c r="O36" s="46"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="1">
-        <v>3</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1</v>
-      </c>
-      <c r="D37" s="1">
-        <f>MAX($I$3,($E$3*C37-$A$6)+(($E$3*C37*$C$6-$A$6)-($E$3*C37-$A$6))*$B$6*B37)</f>
-        <v>1.075</v>
-      </c>
-      <c r="E37" s="9">
-        <f t="shared" si="4"/>
-        <v>3.2249999999999996</v>
-      </c>
-      <c r="F37" s="41"/>
-      <c r="G37" s="46"/>
-      <c r="I37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J37" s="1">
-        <v>10</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0.49399999999999999</v>
-      </c>
-      <c r="L37" s="1">
-        <f t="shared" si="5"/>
-        <v>0.61749999999999994</v>
-      </c>
-      <c r="M37" s="9">
-        <f t="shared" si="6"/>
-        <v>6.1749999999999989</v>
-      </c>
-      <c r="N37" s="40"/>
-      <c r="O37" s="46"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="D38" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38" s="10">
-        <f>SUM(E32:E35)</f>
-        <v>4.3125</v>
-      </c>
-      <c r="F38" s="11">
-        <f>E38/G32</f>
-        <v>2.875</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J38" s="1">
-        <v>2</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0.49399999999999999</v>
-      </c>
-      <c r="L38" s="1">
-        <f t="shared" si="5"/>
-        <v>0.51869999999999994</v>
-      </c>
-      <c r="M38" s="9">
-        <f t="shared" si="6"/>
-        <v>1.0373999999999999</v>
-      </c>
-      <c r="N38" s="41"/>
-      <c r="O38" s="46"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="D39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="10">
-        <f>SUM(E32:E37)</f>
-        <v>9.6374999999999993</v>
-      </c>
-      <c r="F39" s="11">
-        <f>E39/G36</f>
-        <v>3.2124999999999999</v>
-      </c>
-      <c r="I39" s="7"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M39" s="10">
-        <f>SUM(M32:M38)</f>
-        <v>20.314049999999995</v>
-      </c>
-      <c r="N39" s="10">
-        <f>M39/O32</f>
-        <v>5.0785124999999987</v>
-      </c>
-      <c r="O39" s="5"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="E40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A43" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="38"/>
-      <c r="I43" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="J43" s="37"/>
-      <c r="K43" s="37"/>
-      <c r="L43" s="37"/>
-      <c r="M43" s="37"/>
-      <c r="N43" s="38"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A45" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B45" s="1">
-        <v>1</v>
-      </c>
-      <c r="C45" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="D45" s="1">
-        <f>MAX($I$3,($E$3*C45-$A$6)+(($E$3*C45*$C$6-$A$6)-($E$3*C45-$A$6))*$B$6*B45)</f>
-        <v>0.76875000000000004</v>
-      </c>
-      <c r="E45" s="1">
-        <f>D45*B45</f>
-        <v>0.76875000000000004</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="1">
-        <v>1</v>
-      </c>
-      <c r="K45" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="L45" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="M45" s="1">
-        <f t="shared" ref="M45:M49" si="7">L45*J45</f>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N45" s="43">
-        <f>L45+L46+L47</f>
-        <v>0.84000000000000008</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A46" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="1">
-        <v>3</v>
-      </c>
-      <c r="C46" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="D46" s="1">
-        <f>MAX($I$3,($E$3*C46-$A$6)+(($E$3*C46*$C$6-$A$6)-($E$3*C46-$A$6))*$B$6*B46)</f>
-        <v>0.74174999999999991</v>
-      </c>
-      <c r="E46" s="1">
-        <f>D46*B46</f>
-        <v>2.22525</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J46" s="1">
-        <v>1</v>
-      </c>
-      <c r="K46" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="L46" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="M46" s="1">
-        <f t="shared" si="7"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N46" s="44"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A47" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="1">
-        <v>2</v>
-      </c>
-      <c r="C47" s="1">
-        <v>0.85</v>
-      </c>
-      <c r="D47" s="1">
-        <f>MAX($I$3,($E$3*C47-$A$6)+(($E$3*C47*$C$6-$A$6)-($E$3*C47-$A$6))*$B$6*B47)</f>
-        <v>0.89249999999999996</v>
-      </c>
-      <c r="E47" s="1">
-        <f>D47*B47</f>
-        <v>1.7849999999999999</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J47" s="1">
-        <v>2</v>
-      </c>
-      <c r="K47" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="L47" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="M47" s="1">
-        <f t="shared" si="7"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="N47" s="45"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A48" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" s="1">
-        <v>2</v>
-      </c>
-      <c r="C48" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="D48" s="1">
-        <f>MAX($I$3,($E$3*C48-$A$6)+(($E$3*C48*$C$6-$A$6)-($E$3*C48-$A$6))*$B$6*B48)</f>
-        <v>0.72449999999999992</v>
-      </c>
-      <c r="E48" s="1">
-        <f>D48*B48</f>
-        <v>1.4489999999999998</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J48" s="1">
-        <v>2</v>
-      </c>
-      <c r="K48" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="L48" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="M48" s="1">
-        <f t="shared" si="7"/>
-        <v>0.68</v>
-      </c>
-      <c r="N48" s="43">
-        <f>L45+L46+L48+L49</f>
-        <v>1.2400000000000002</v>
-      </c>
-    </row>
-    <row r="49" spans="9:14" x14ac:dyDescent="0.15">
-      <c r="I49" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J49" s="1">
-        <v>2</v>
-      </c>
-      <c r="K49" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="L49" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="M49" s="1">
-        <f t="shared" si="7"/>
-        <v>0.68</v>
-      </c>
-      <c r="N49" s="45"/>
-    </row>
-  </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="N45:N47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="O32:O38"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="N32:N38"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="V10:V12"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="O10:O16"/>
-    <mergeCell ref="N10:N16"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="I20:N20"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:W1"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="I8:N8"/>
-    <mergeCell ref="Q8:V8"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:AZ21"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2572,57 +1983,57 @@
     </row>
     <row r="3" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="21"/>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
-      <c r="V3" s="50" t="s">
+      <c r="V3" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="50"/>
-      <c r="AD3" s="50"/>
-      <c r="AE3" s="50"/>
-      <c r="AF3" s="50"/>
-      <c r="AG3" s="50"/>
-      <c r="AH3" s="50"/>
-      <c r="AI3" s="50"/>
-      <c r="AJ3" s="50"/>
-      <c r="AK3" s="50"/>
-      <c r="AL3" s="50"/>
-      <c r="AM3" s="50"/>
-      <c r="AN3" s="50"/>
-      <c r="AO3" s="50"/>
-      <c r="AP3" s="50"/>
-      <c r="AQ3" s="50"/>
-      <c r="AR3" s="50"/>
-      <c r="AS3" s="50"/>
-      <c r="AT3" s="50"/>
-      <c r="AU3" s="50"/>
-      <c r="AV3" s="50"/>
-      <c r="AW3" s="50"/>
-      <c r="AX3" s="50"/>
-      <c r="AY3" s="50"/>
+      <c r="W3" s="48"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="48"/>
+      <c r="Z3" s="48"/>
+      <c r="AA3" s="48"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="48"/>
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="48"/>
+      <c r="AI3" s="48"/>
+      <c r="AJ3" s="48"/>
+      <c r="AK3" s="48"/>
+      <c r="AL3" s="48"/>
+      <c r="AM3" s="48"/>
+      <c r="AN3" s="48"/>
+      <c r="AO3" s="48"/>
+      <c r="AP3" s="48"/>
+      <c r="AQ3" s="48"/>
+      <c r="AR3" s="48"/>
+      <c r="AS3" s="48"/>
+      <c r="AT3" s="48"/>
+      <c r="AU3" s="48"/>
+      <c r="AV3" s="48"/>
+      <c r="AW3" s="48"/>
+      <c r="AX3" s="48"/>
+      <c r="AY3" s="48"/>
       <c r="AZ3" s="21"/>
     </row>
     <row r="4" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2668,44 +2079,44 @@
       <c r="R4" s="21"/>
       <c r="S4" s="21"/>
       <c r="T4" s="21"/>
-      <c r="V4" s="51" t="s">
+      <c r="V4" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="51"/>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
+      <c r="W4" s="49"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="49"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="51" t="s">
+      <c r="AD4" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="51"/>
+      <c r="AE4" s="49"/>
+      <c r="AF4" s="49"/>
+      <c r="AG4" s="49"/>
       <c r="AH4" s="21"/>
       <c r="AI4" s="21"/>
       <c r="AJ4" s="21"/>
       <c r="AK4" s="21"/>
-      <c r="AL4" s="51" t="s">
+      <c r="AL4" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="AM4" s="51"/>
-      <c r="AN4" s="51"/>
-      <c r="AO4" s="51"/>
-      <c r="AP4" s="51"/>
-      <c r="AQ4" s="51"/>
+      <c r="AM4" s="49"/>
+      <c r="AN4" s="49"/>
+      <c r="AO4" s="49"/>
+      <c r="AP4" s="49"/>
+      <c r="AQ4" s="49"/>
       <c r="AR4" s="21"/>
       <c r="AS4" s="21"/>
-      <c r="AT4" s="51" t="s">
+      <c r="AT4" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="AU4" s="51"/>
-      <c r="AV4" s="51"/>
-      <c r="AW4" s="51"/>
-      <c r="AX4" s="51"/>
-      <c r="AY4" s="51"/>
+      <c r="AU4" s="49"/>
+      <c r="AV4" s="49"/>
+      <c r="AW4" s="49"/>
+      <c r="AX4" s="49"/>
+      <c r="AY4" s="49"/>
       <c r="AZ4" s="21"/>
     </row>
     <row r="5" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -2847,7 +2258,7 @@
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="48">
+      <c r="B6" s="50">
         <v>0</v>
       </c>
       <c r="C6" s="19">
@@ -2910,6 +2321,9 @@
         <f>K6/S6</f>
         <v>5.5</v>
       </c>
+      <c r="U6" s="8">
+        <v>0</v>
+      </c>
       <c r="V6" s="12">
         <v>6</v>
       </c>
@@ -3008,7 +2422,7 @@
       </c>
     </row>
     <row r="7" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="48"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="19">
         <v>1.1000000000000001</v>
       </c>
@@ -3069,6 +2483,9 @@
         <f>K7/S7</f>
         <v>5.2083333333333339</v>
       </c>
+      <c r="U7" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="V7" s="12">
         <v>12</v>
       </c>
@@ -3167,7 +2584,7 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="48">
+      <c r="B8" s="50">
         <v>1</v>
       </c>
       <c r="C8" s="18">
@@ -3230,6 +2647,9 @@
         <f>K8/S8</f>
         <v>5.5285272003538264</v>
       </c>
+      <c r="U8" s="8">
+        <v>1</v>
+      </c>
       <c r="V8" s="12">
         <v>23</v>
       </c>
@@ -3328,7 +2748,7 @@
       </c>
     </row>
     <row r="9" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="48"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="19">
         <v>1.3</v>
       </c>
@@ -3389,6 +2809,9 @@
         <f>K9/S9</f>
         <v>5.2526525895577274</v>
       </c>
+      <c r="U9" s="52" t="s">
+        <v>92</v>
+      </c>
       <c r="V9" s="12">
         <v>38</v>
       </c>
@@ -3487,7 +2910,7 @@
       </c>
     </row>
     <row r="10" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="49">
+      <c r="B10" s="51">
         <v>2</v>
       </c>
       <c r="C10" s="18">
@@ -3550,6 +2973,9 @@
         <f>K10/S10</f>
         <v>5.2615289384091612</v>
       </c>
+      <c r="U10" s="7" t="s">
+        <v>92</v>
+      </c>
       <c r="V10" s="12">
         <v>58</v>
       </c>
@@ -3648,10 +3074,10 @@
       </c>
     </row>
     <row r="11" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="49"/>
+      <c r="B11" s="51"/>
     </row>
     <row r="12" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="49"/>
+      <c r="B12" s="51"/>
       <c r="C12" s="19">
         <v>2.1</v>
       </c>
@@ -3712,6 +3138,9 @@
         <f>K12/S12</f>
         <v>5.3571428571428577</v>
       </c>
+      <c r="U12" s="7" t="s">
+        <v>92</v>
+      </c>
       <c r="V12" s="12">
         <v>110</v>
       </c>
@@ -3810,7 +3239,7 @@
       </c>
     </row>
     <row r="13" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="48">
+      <c r="B13" s="50">
         <v>3</v>
       </c>
       <c r="C13" s="18">
@@ -3873,6 +3302,9 @@
         <f>K13/S13</f>
         <v>5.3344867358708186</v>
       </c>
+      <c r="U13" s="8">
+        <v>2</v>
+      </c>
       <c r="V13" s="12">
         <v>165</v>
       </c>
@@ -3971,7 +3403,7 @@
       </c>
     </row>
     <row r="14" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="48"/>
+      <c r="B14" s="50"/>
       <c r="C14" s="19">
         <v>2.2999999999999998</v>
       </c>
@@ -4032,6 +3464,9 @@
         <f>K14/S14</f>
         <v>5.3185831294543133</v>
       </c>
+      <c r="U14" s="7" t="s">
+        <v>94</v>
+      </c>
       <c r="V14" s="12">
         <v>230</v>
       </c>
@@ -4130,7 +3565,7 @@
       </c>
     </row>
     <row r="16" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="48">
+      <c r="B16" s="50">
         <v>4</v>
       </c>
       <c r="C16" s="19">
@@ -4193,6 +3628,9 @@
         <f>K16/S16</f>
         <v>4.8828125</v>
       </c>
+      <c r="U16" s="8">
+        <v>3</v>
+      </c>
       <c r="V16" s="12">
         <v>350</v>
       </c>
@@ -4291,7 +3729,7 @@
       </c>
     </row>
     <row r="17" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="48"/>
+      <c r="B17" s="50"/>
       <c r="C17" s="18">
         <v>3.2</v>
       </c>
@@ -4352,6 +3790,9 @@
         <f>K17/S17</f>
         <v>4.821600771456124</v>
       </c>
+      <c r="U17" s="7" t="s">
+        <v>95</v>
+      </c>
       <c r="V17" s="12">
         <v>460</v>
       </c>
@@ -4450,7 +3891,7 @@
       </c>
     </row>
     <row r="18" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="48"/>
+      <c r="B18" s="50"/>
       <c r="C18" s="19">
         <v>3.3</v>
       </c>
@@ -4511,6 +3952,9 @@
         <f>K18/S18</f>
         <v>4.62242117555469</v>
       </c>
+      <c r="U18" s="7" t="s">
+        <v>95</v>
+      </c>
       <c r="V18" s="12">
         <v>620</v>
       </c>
@@ -4609,7 +4053,7 @@
       </c>
     </row>
     <row r="20" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="48">
+      <c r="B20" s="50">
         <v>5</v>
       </c>
       <c r="C20" s="18">
@@ -4672,6 +4116,9 @@
         <f>K20/S20</f>
         <v>4.0275950073772782</v>
       </c>
+      <c r="U20" s="8">
+        <v>4</v>
+      </c>
       <c r="V20" s="12">
         <v>800</v>
       </c>
@@ -4770,7 +4217,7 @@
       </c>
     </row>
     <row r="21" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="48"/>
+      <c r="B21" s="50"/>
       <c r="C21" s="19">
         <v>4.2</v>
       </c>
@@ -4831,6 +4278,9 @@
         <f>K21/S21</f>
         <v>3.9295392953929538</v>
       </c>
+      <c r="U21" s="8">
+        <v>5</v>
+      </c>
       <c r="V21" s="12">
         <v>1150</v>
       </c>
@@ -4930,18 +4380,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="D3:P3"/>
     <mergeCell ref="V3:AY3"/>
     <mergeCell ref="AT4:AY4"/>
     <mergeCell ref="AL4:AQ4"/>
     <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="V4:AA4"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B18"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4949,13 +4399,2171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F2A8C5-C710-4410-8433-B168C3A556B3}">
+  <dimension ref="A1:U24"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="12.625" style="5" customWidth="1"/>
+    <col min="2" max="4" width="16.625" style="5" customWidth="1"/>
+    <col min="5" max="8" width="16.625" style="5"/>
+    <col min="9" max="9" width="8.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="2.625" style="5" customWidth="1"/>
+    <col min="11" max="14" width="16.625" style="5"/>
+    <col min="15" max="15" width="8.625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="2.625" style="5" customWidth="1"/>
+    <col min="17" max="20" width="16.625" style="5"/>
+    <col min="21" max="21" width="8.625" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="16.625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E1" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="54" t="s">
+        <v>160</v>
+      </c>
+      <c r="K1" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="56" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q1" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="58" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="60" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="110" t="s">
+        <v>197</v>
+      </c>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110" t="s">
+        <v>198</v>
+      </c>
+      <c r="H2" s="110"/>
+      <c r="K2" s="110" t="s">
+        <v>197</v>
+      </c>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110" t="s">
+        <v>198</v>
+      </c>
+      <c r="N2" s="110"/>
+      <c r="Q2" s="110" t="s">
+        <v>197</v>
+      </c>
+      <c r="R2" s="110"/>
+      <c r="S2" s="110" t="s">
+        <v>198</v>
+      </c>
+      <c r="T2" s="110"/>
+    </row>
+    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="76">
+        <v>0.1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="87" t="s">
+        <v>129</v>
+      </c>
+      <c r="K3" s="62"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="86" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="71" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="83">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="88"/>
+      <c r="K4" s="92" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92" t="s">
+        <v>134</v>
+      </c>
+      <c r="N4" s="90"/>
+      <c r="O4" s="78">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="68"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="70"/>
+      <c r="U4" s="61"/>
+    </row>
+    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="83">
+        <v>1.2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="89" t="s">
+        <v>196</v>
+      </c>
+      <c r="F5" s="89" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="89" t="s">
+        <v>131</v>
+      </c>
+      <c r="H5" s="91" t="s">
+        <v>132</v>
+      </c>
+      <c r="I5" s="72">
+        <v>0</v>
+      </c>
+      <c r="K5" s="91" t="s">
+        <v>194</v>
+      </c>
+      <c r="L5" s="91"/>
+      <c r="M5" s="91" t="s">
+        <v>195</v>
+      </c>
+      <c r="N5" s="90"/>
+      <c r="O5" s="79"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="70"/>
+      <c r="U5" s="61"/>
+    </row>
+    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="83">
+        <v>1.3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="91" t="s">
+        <v>161</v>
+      </c>
+      <c r="H6" s="90"/>
+      <c r="I6" s="72"/>
+      <c r="K6" s="91" t="s">
+        <v>166</v>
+      </c>
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="79"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="61"/>
+    </row>
+    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="83">
+        <v>1.4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="91" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91" t="s">
+        <v>165</v>
+      </c>
+      <c r="H7" s="90"/>
+      <c r="I7" s="72"/>
+      <c r="K7" s="91" t="s">
+        <v>168</v>
+      </c>
+      <c r="L7" s="91"/>
+      <c r="M7" s="90" t="s">
+        <v>167</v>
+      </c>
+      <c r="N7" s="90"/>
+      <c r="O7" s="80"/>
+      <c r="Q7" s="97" t="s">
+        <v>135</v>
+      </c>
+      <c r="R7" s="97" t="s">
+        <v>136</v>
+      </c>
+      <c r="S7" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="T7" s="94" t="s">
+        <v>174</v>
+      </c>
+      <c r="U7" s="73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="77">
+        <v>2.1</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="91"/>
+      <c r="G8" s="90" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" s="90"/>
+      <c r="I8" s="72"/>
+      <c r="K8" s="96" t="s">
+        <v>137</v>
+      </c>
+      <c r="L8" s="96" t="s">
+        <v>138</v>
+      </c>
+      <c r="M8" s="96" t="s">
+        <v>155</v>
+      </c>
+      <c r="N8" s="94" t="s">
+        <v>171</v>
+      </c>
+      <c r="O8" s="73">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="94" t="s">
+        <v>172</v>
+      </c>
+      <c r="R8" s="94"/>
+      <c r="S8" s="94" t="s">
+        <v>173</v>
+      </c>
+      <c r="T8" s="94" t="s">
+        <v>199</v>
+      </c>
+      <c r="U8" s="73"/>
+    </row>
+    <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="77">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="93" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="93" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9" s="93" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="93" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="73">
+        <v>1</v>
+      </c>
+      <c r="K9" s="94" t="s">
+        <v>177</v>
+      </c>
+      <c r="L9" s="94" t="s">
+        <v>178</v>
+      </c>
+      <c r="M9" s="94" t="s">
+        <v>179</v>
+      </c>
+      <c r="N9" s="94" t="s">
+        <v>180</v>
+      </c>
+      <c r="O9" s="73"/>
+      <c r="Q9" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="R9" s="33"/>
+      <c r="S9" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="T9" s="99"/>
+      <c r="U9" s="74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="77">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="94" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" s="95"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="73"/>
+      <c r="K10" s="100" t="s">
+        <v>142</v>
+      </c>
+      <c r="L10" s="100"/>
+      <c r="M10" s="100" t="s">
+        <v>156</v>
+      </c>
+      <c r="N10" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="O10" s="74">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="R10" s="99"/>
+      <c r="S10" s="99"/>
+      <c r="T10" s="99"/>
+      <c r="U10" s="74"/>
+    </row>
+    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="111">
+        <v>3.1</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="98" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="98" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" s="98" t="s">
+        <v>145</v>
+      </c>
+      <c r="H11" s="98" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" s="74">
+        <v>2</v>
+      </c>
+      <c r="K11" s="33"/>
+      <c r="L11" s="99"/>
+      <c r="M11" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="N11" s="99"/>
+      <c r="O11" s="74"/>
+      <c r="Q11" s="104" t="s">
+        <v>184</v>
+      </c>
+      <c r="R11" s="104"/>
+      <c r="S11" s="104" t="s">
+        <v>186</v>
+      </c>
+      <c r="T11" s="102"/>
+      <c r="U11" s="75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="111">
+        <v>3.2</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="H12" s="99"/>
+      <c r="I12" s="74"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="N12" s="99"/>
+      <c r="O12" s="74"/>
+      <c r="Q12" s="105" t="s">
+        <v>153</v>
+      </c>
+      <c r="R12" s="102"/>
+      <c r="S12" s="102"/>
+      <c r="T12" s="102"/>
+      <c r="U12" s="75"/>
+    </row>
+    <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="111">
+        <v>3.3</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="74"/>
+      <c r="K13" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="L13" s="103" t="s">
+        <v>148</v>
+      </c>
+      <c r="M13" s="104" t="s">
+        <v>189</v>
+      </c>
+      <c r="N13" s="104" t="s">
+        <v>191</v>
+      </c>
+      <c r="O13" s="77">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="R13" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="S13" s="107"/>
+      <c r="T13" s="107"/>
+      <c r="U13" s="81">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="82">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="101" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14" s="101"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="75">
+        <v>3</v>
+      </c>
+      <c r="K14" s="106"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="N14" s="107"/>
+      <c r="O14" s="84">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="R14" s="107"/>
+      <c r="S14" s="107"/>
+      <c r="T14" s="107"/>
+      <c r="U14" s="81"/>
+    </row>
+    <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="82">
+        <v>4.2</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="101" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="75"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="107"/>
+      <c r="M15" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="N15" s="107"/>
+      <c r="O15" s="85"/>
+      <c r="Q15" s="108" t="s">
+        <v>153</v>
+      </c>
+      <c r="R15" s="109"/>
+      <c r="S15" s="109"/>
+      <c r="T15" s="109"/>
+      <c r="U15" s="82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C18" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="42"/>
+    </row>
+    <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E3:H4"/>
+    <mergeCell ref="Q3:T6"/>
+    <mergeCell ref="O4:O7"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="U3:U6"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="O10:O12"/>
+    <mergeCell ref="C18:D18"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <cols>
+    <col min="5" max="5" width="10.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="G1" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9">
+        <f>A3+B3+(C3/2)+D3</f>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A6" s="1">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A8" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="4"/>
+      <c r="I8" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="1"/>
+      <c r="Q8" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="R8" s="37"/>
+      <c r="S8" s="37"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="38"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="D10" s="1">
+        <f>MAX($I$3,($E$3*C10-$A$6)+(($E$3*C10*$C$6-$A$6)-($E$3*C10-$A$6))*$B$6)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" ref="E10:E15" si="0">D10*B10</f>
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="43">
+        <f>D10+D11+D12+D13</f>
+        <v>2</v>
+      </c>
+      <c r="G10" s="42">
+        <v>1.5</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" ref="L10:L16" si="1">MAX($I$3,($E$3*K10-$A$6)+(($E$3*K10*$C$6-$A$6)-($E$3*K10-$A$6))*$B$6*J10)</f>
+        <v>0.5</v>
+      </c>
+      <c r="M10" s="9">
+        <f t="shared" ref="M10:M16" si="2">L10*J10</f>
+        <v>0.5</v>
+      </c>
+      <c r="N10" s="43">
+        <f>L10+L11+L12+L13+L14+L15+L16</f>
+        <v>3.5</v>
+      </c>
+      <c r="O10" s="42">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R10" s="1">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="T10" s="1">
+        <f>MAX($I$3,($E$3*S10-$A$6)+(($E$3*S10*$C$6-$A$6)-($E$3*S10-$A$6))*$B$6*R10)</f>
+        <v>0.5</v>
+      </c>
+      <c r="U10" s="1">
+        <f>T10*R10</f>
+        <v>0.5</v>
+      </c>
+      <c r="V10" s="39">
+        <f>T10+T11+T12</f>
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="D11" s="1">
+        <f>MAX($I$3,($E$3*C11-$A$6)+(($E$3*C11*$C$6-$A$6)-($E$3*C11-$A$6))*$B$6*B11)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="9">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="46"/>
+      <c r="G11" s="42"/>
+      <c r="I11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="9">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="N11" s="46"/>
+      <c r="O11" s="42"/>
+      <c r="Q11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="T11" s="1">
+        <f>MAX($I$3,($E$3*S11-$A$6)+(($E$3*S11*$C$6-$A$6)-($E$3*S11-$A$6))*$B$6*R11)</f>
+        <v>0.5</v>
+      </c>
+      <c r="U11" s="1">
+        <f>T11*R11</f>
+        <v>0.5</v>
+      </c>
+      <c r="V11" s="40"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="D12" s="1">
+        <f>MAX($I$3,($E$3*C12-$A$6)+(($E$3*C12*$C$6-$A$6)-($E$3*C12-$A$6))*$B$6*B12)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F12" s="46"/>
+      <c r="G12" s="42"/>
+      <c r="I12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="L12" s="1">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="46"/>
+      <c r="O12" s="42"/>
+      <c r="Q12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" s="1">
+        <v>2</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="T12" s="1">
+        <f>MAX($I$3,($E$3*S12-$A$6)+(($E$3*S12*$C$6-$A$6)-($E$3*S12-$A$6))*$B$6*R12)</f>
+        <v>0.84000000000000008</v>
+      </c>
+      <c r="U12" s="1">
+        <f>T12*R12</f>
+        <v>1.6800000000000002</v>
+      </c>
+      <c r="V12" s="41"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="D13" s="1">
+        <f>MAX($I$3,($E$3*C13-$A$6)+(($E$3*C13*$C$6-$A$6)-($E$3*C13-$A$6))*$B$6*B13)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="42"/>
+      <c r="I13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="1">
+        <v>10</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="L13" s="1">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="M13" s="9">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="N13" s="46"/>
+      <c r="O13" s="42"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D14" s="1">
+        <f>MAX($I$3,($E$3*C14-$A$6)+(($E$3*C14*$C$6-$A$6)-($E$3*C14-$A$6))*$B$6*B14)</f>
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="E14" s="9">
+        <f t="shared" si="0"/>
+        <v>1.575</v>
+      </c>
+      <c r="F14" s="43">
+        <f>D10+D11+D12+D14+D15</f>
+        <v>3.09375</v>
+      </c>
+      <c r="G14" s="42">
+        <v>3</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="1">
+        <v>7</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="9">
+        <f t="shared" si="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="N14" s="46"/>
+      <c r="O14" s="42"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D15" s="1">
+        <f>MAX($I$3,($E$3*C15-$A$6)+(($E$3*C15*$C$6-$A$6)-($E$3*C15-$A$6))*$B$6*B15)</f>
+        <v>0.80625000000000002</v>
+      </c>
+      <c r="E15" s="9">
+        <f t="shared" si="0"/>
+        <v>2.4187500000000002</v>
+      </c>
+      <c r="F15" s="44"/>
+      <c r="G15" s="42"/>
+      <c r="I15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="1">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="L15" s="1">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="M15" s="9">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="N15" s="46"/>
+      <c r="O15" s="42"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="D16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="10">
+        <f>SUM(E10:E13)</f>
+        <v>3</v>
+      </c>
+      <c r="F16" s="11">
+        <f>E16/G10</f>
+        <v>2</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N16" s="44"/>
+      <c r="O16" s="42"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="D17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="10">
+        <f>SUM(E10:E15)</f>
+        <v>6.9937500000000004</v>
+      </c>
+      <c r="F17" s="11">
+        <f>E17/G14</f>
+        <v>2.3312500000000003</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M17" s="10">
+        <f>SUM(M10:M16)</f>
+        <v>16.5</v>
+      </c>
+      <c r="N17" s="10">
+        <f>M17/O10</f>
+        <v>4.125</v>
+      </c>
+      <c r="O17" s="5"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="E18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A20" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
+      <c r="I20" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="5"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O21" s="5"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="1">
+        <f>MAX($I$3,($E$3*C22-$A$6)+(($E$3*C22*$C$6-$A$6)-($E$3*C22-$A$6))*$B$6*B22)</f>
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="E22" s="1">
+        <f>D22*B22</f>
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M22" s="1">
+        <f t="shared" ref="M22:M26" si="3">L22*J22</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N22" s="39">
+        <f>L22+L23+L24</f>
+        <v>0.84000000000000008</v>
+      </c>
+      <c r="O22" s="5"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="1">
+        <v>3</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="D23" s="1">
+        <f>MAX($I$3,($E$3*C23-$A$6)+(($E$3*C23*$C$6-$A$6)-($E$3*C23-$A$6))*$B$6*B23)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="1">
+        <f>D23*B23</f>
+        <v>1.5</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M23" s="1">
+        <f t="shared" si="3"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N23" s="40"/>
+      <c r="O23" s="5"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D24" s="1">
+        <f>MAX($I$3,($E$3*C24-$A$6)+(($E$3*C24*$C$6-$A$6)-($E$3*C24-$A$6))*$B$6*B24)</f>
+        <v>0.63</v>
+      </c>
+      <c r="E24" s="1">
+        <f>D24*B24</f>
+        <v>1.26</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M24" s="1">
+        <f t="shared" si="3"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="N24" s="41"/>
+      <c r="O24" s="5"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="D25" s="1">
+        <f>MAX($I$3,($E$3*C25-$A$6)+(($E$3*C25*$C$6-$A$6)-($E$3*C25-$A$6))*$B$6*B25)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="1">
+        <f>D25*B25</f>
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="M25" s="1">
+        <f t="shared" si="3"/>
+        <v>0.68</v>
+      </c>
+      <c r="N25" s="39">
+        <f>L22+L23+L25+L26</f>
+        <v>1.2400000000000002</v>
+      </c>
+      <c r="O25" s="5"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="I26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="1">
+        <v>2</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="3"/>
+        <v>0.68</v>
+      </c>
+      <c r="N26" s="41"/>
+      <c r="O26" s="5"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A29">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A30" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="4"/>
+      <c r="I30" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
+      <c r="M30" s="37"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D32" s="1">
+        <f>MAX($I$3,($E$3*C32-$A$6)+(($E$3*C32*$C$6-$A$6)-($E$3*C32-$A$6))*$B$6)</f>
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="E32" s="9">
+        <f t="shared" ref="E32:E37" si="4">D32*B32</f>
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="F32" s="43">
+        <f>D32+D33+D34+D35</f>
+        <v>2.8634999999999997</v>
+      </c>
+      <c r="G32" s="42">
+        <v>1.5</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" ref="L32:L38" si="5">MAX($I$3,($E$3*K32-$A$6)+(($E$3*K32*$C$6-$A$6)-($E$3*K32-$A$6))*$B$6*J32)</f>
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="M32" s="9">
+        <f t="shared" ref="M32:M38" si="6">L32*J32</f>
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="N32" s="43">
+        <f>L32+L33+L34+L35+L36+L37+L38</f>
+        <v>4.4731499999999995</v>
+      </c>
+      <c r="O32" s="42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D33" s="1">
+        <f>MAX($I$3,($E$3*C33-$A$6)+(($E$3*C33*$C$6-$A$6)-($E$3*C33-$A$6))*$B$6*B33)</f>
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="E33" s="9">
+        <f t="shared" si="4"/>
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="F33" s="46"/>
+      <c r="G33" s="42"/>
+      <c r="I33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="L33" s="1">
+        <f t="shared" si="5"/>
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="M33" s="9">
+        <f t="shared" si="6"/>
+        <v>0.70724999999999993</v>
+      </c>
+      <c r="N33" s="46"/>
+      <c r="O33" s="42"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="1">
+        <v>2</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D34" s="1">
+        <f>MAX($I$3,($E$3*C34-$A$6)+(($E$3*C34*$C$6-$A$6)-($E$3*C34-$A$6))*$B$6*B34)</f>
+        <v>0.72449999999999992</v>
+      </c>
+      <c r="E34" s="9">
+        <f t="shared" si="4"/>
+        <v>1.4489999999999998</v>
+      </c>
+      <c r="F34" s="46"/>
+      <c r="G34" s="42"/>
+      <c r="I34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="L34" s="1">
+        <f t="shared" si="5"/>
+        <v>0.72449999999999992</v>
+      </c>
+      <c r="M34" s="9">
+        <f t="shared" si="6"/>
+        <v>1.4489999999999998</v>
+      </c>
+      <c r="N34" s="46"/>
+      <c r="O34" s="42"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="1">
+        <v>2</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D35" s="1">
+        <f>MAX($I$3,($E$3*C35-$A$6)+(($E$3*C35*$C$6-$A$6)-($E$3*C35-$A$6))*$B$6*B35)</f>
+        <v>0.72449999999999992</v>
+      </c>
+      <c r="E35" s="9">
+        <f t="shared" si="4"/>
+        <v>1.4489999999999998</v>
+      </c>
+      <c r="F35" s="44"/>
+      <c r="G35" s="42"/>
+      <c r="I35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="1">
+        <v>10</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="L35" s="1">
+        <f t="shared" si="5"/>
+        <v>0.61749999999999994</v>
+      </c>
+      <c r="M35" s="9">
+        <f t="shared" si="6"/>
+        <v>6.1749999999999989</v>
+      </c>
+      <c r="N35" s="46"/>
+      <c r="O35" s="42"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="1">
+        <v>2</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="1">
+        <f>MAX($I$3,($E$3*C36-$A$6)+(($E$3*C36*$C$6-$A$6)-($E$3*C36-$A$6))*$B$6*B36)</f>
+        <v>1.05</v>
+      </c>
+      <c r="E36" s="9">
+        <f t="shared" si="4"/>
+        <v>2.1</v>
+      </c>
+      <c r="F36" s="43">
+        <f>D32+D33+D34+D36+D37</f>
+        <v>4.2640000000000002</v>
+      </c>
+      <c r="G36" s="42">
+        <v>3</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" s="1">
+        <v>7</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="L36" s="1">
+        <f t="shared" si="5"/>
+        <v>0.58045000000000002</v>
+      </c>
+      <c r="M36" s="9">
+        <f t="shared" si="6"/>
+        <v>4.0631500000000003</v>
+      </c>
+      <c r="N36" s="46"/>
+      <c r="O36" s="42"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1">
+        <f>MAX($I$3,($E$3*C37-$A$6)+(($E$3*C37*$C$6-$A$6)-($E$3*C37-$A$6))*$B$6*B37)</f>
+        <v>1.075</v>
+      </c>
+      <c r="E37" s="9">
+        <f t="shared" si="4"/>
+        <v>3.2249999999999996</v>
+      </c>
+      <c r="F37" s="44"/>
+      <c r="G37" s="42"/>
+      <c r="I37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J37" s="1">
+        <v>10</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="L37" s="1">
+        <f t="shared" si="5"/>
+        <v>0.61749999999999994</v>
+      </c>
+      <c r="M37" s="9">
+        <f t="shared" si="6"/>
+        <v>6.1749999999999989</v>
+      </c>
+      <c r="N37" s="46"/>
+      <c r="O37" s="42"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="D38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" s="10">
+        <f>SUM(E32:E35)</f>
+        <v>4.3125</v>
+      </c>
+      <c r="F38" s="11">
+        <f>E38/G32</f>
+        <v>2.875</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J38" s="1">
+        <v>2</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="L38" s="1">
+        <f t="shared" si="5"/>
+        <v>0.51869999999999994</v>
+      </c>
+      <c r="M38" s="9">
+        <f t="shared" si="6"/>
+        <v>1.0373999999999999</v>
+      </c>
+      <c r="N38" s="44"/>
+      <c r="O38" s="42"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="D39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="10">
+        <f>SUM(E32:E37)</f>
+        <v>9.6374999999999993</v>
+      </c>
+      <c r="F39" s="11">
+        <f>E39/G36</f>
+        <v>3.2124999999999999</v>
+      </c>
+      <c r="I39" s="7"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M39" s="10">
+        <f>SUM(M32:M38)</f>
+        <v>20.314049999999995</v>
+      </c>
+      <c r="N39" s="10">
+        <f>M39/O32</f>
+        <v>5.0785124999999987</v>
+      </c>
+      <c r="O39" s="5"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="E40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A43" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="38"/>
+      <c r="I43" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="J43" s="37"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="37"/>
+      <c r="M43" s="37"/>
+      <c r="N43" s="38"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D45" s="1">
+        <f>MAX($I$3,($E$3*C45-$A$6)+(($E$3*C45*$C$6-$A$6)-($E$3*C45-$A$6))*$B$6*B45)</f>
+        <v>0.76875000000000004</v>
+      </c>
+      <c r="E45" s="1">
+        <f>D45*B45</f>
+        <v>0.76875000000000004</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M45" s="1">
+        <f t="shared" ref="M45:M49" si="7">L45*J45</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N45" s="39">
+        <f>L45+L46+L47</f>
+        <v>0.84000000000000008</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A46" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B46" s="1">
+        <v>3</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D46" s="1">
+        <f>MAX($I$3,($E$3*C46-$A$6)+(($E$3*C46*$C$6-$A$6)-($E$3*C46-$A$6))*$B$6*B46)</f>
+        <v>0.74174999999999991</v>
+      </c>
+      <c r="E46" s="1">
+        <f>D46*B46</f>
+        <v>2.22525</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M46" s="1">
+        <f t="shared" si="7"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N46" s="40"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" s="1">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="D47" s="1">
+        <f>MAX($I$3,($E$3*C47-$A$6)+(($E$3*C47*$C$6-$A$6)-($E$3*C47-$A$6))*$B$6*B47)</f>
+        <v>0.89249999999999996</v>
+      </c>
+      <c r="E47" s="1">
+        <f>D47*B47</f>
+        <v>1.7849999999999999</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="1">
+        <v>2</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M47" s="1">
+        <f t="shared" si="7"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="N47" s="41"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A48" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" s="1">
+        <v>2</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D48" s="1">
+        <f>MAX($I$3,($E$3*C48-$A$6)+(($E$3*C48*$C$6-$A$6)-($E$3*C48-$A$6))*$B$6*B48)</f>
+        <v>0.72449999999999992</v>
+      </c>
+      <c r="E48" s="1">
+        <f>D48*B48</f>
+        <v>1.4489999999999998</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="1">
+        <v>2</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="M48" s="1">
+        <f t="shared" si="7"/>
+        <v>0.68</v>
+      </c>
+      <c r="N48" s="39">
+        <f>L45+L46+L48+L49</f>
+        <v>1.2400000000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="9:14" x14ac:dyDescent="0.15">
+      <c r="I49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" s="1">
+        <v>2</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="M49" s="1">
+        <f t="shared" si="7"/>
+        <v>0.68</v>
+      </c>
+      <c r="N49" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="I20:N20"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:W1"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="Q8:V8"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="V10:V12"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="O10:O16"/>
+    <mergeCell ref="N10:N16"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="N32:N38"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="I43:N43"/>
+    <mergeCell ref="N45:N47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="O32:O38"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>